--- a/doc/SV500_Route_Map_20260615.xlsx
+++ b/doc/SV500_Route_Map_20260615.xlsx
@@ -654,7 +654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H372"/>
+  <dimension ref="A1:H373"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -8612,7 +8612,7 @@
       </c>
       <c r="D207" s="3" t="inlineStr">
         <is>
-          <t>store/auth.js</t>
+          <t>partials/inners/trend/HarmonicsTab.vue</t>
         </is>
       </c>
       <c r="E207" s="4" t="inlineStr">
@@ -8622,17 +8622,17 @@
       </c>
       <c r="F207" s="5" t="inlineStr">
         <is>
-          <t>/auth/checkLogins</t>
+          <t>/api/getHarmonicsTrend/{channel}</t>
         </is>
       </c>
       <c r="G207" s="5" t="inlineStr">
         <is>
-          <t>routes/auth.py</t>
+          <t>routes/api.py</t>
         </is>
       </c>
       <c r="H207" s="3" t="inlineStr">
         <is>
-          <t>checkLogins</t>
+          <t>getHarmonicsTrend</t>
         </is>
       </c>
     </row>
@@ -8657,12 +8657,12 @@
       </c>
       <c r="E208" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="F208" s="5" t="inlineStr">
         <is>
-          <t>/auth/logout</t>
+          <t>/auth/checkLogins</t>
         </is>
       </c>
       <c r="G208" s="5" t="inlineStr">
@@ -8672,7 +8672,7 @@
       </c>
       <c r="H208" s="3" t="inlineStr">
         <is>
-          <t>logout</t>
+          <t>checkLogins</t>
         </is>
       </c>
     </row>
@@ -8702,7 +8702,7 @@
       </c>
       <c r="F209" s="5" t="inlineStr">
         <is>
-          <t>/auth/checkSession</t>
+          <t>/auth/logout</t>
         </is>
       </c>
       <c r="G209" s="5" t="inlineStr">
@@ -8712,7 +8712,7 @@
       </c>
       <c r="H209" s="3" t="inlineStr">
         <is>
-          <t>check_session</t>
+          <t>logout</t>
         </is>
       </c>
     </row>
@@ -8742,7 +8742,7 @@
       </c>
       <c r="F210" s="5" t="inlineStr">
         <is>
-          <t>/auth/checkInstall</t>
+          <t>/auth/checkSession</t>
         </is>
       </c>
       <c r="G210" s="5" t="inlineStr">
@@ -8752,7 +8752,7 @@
       </c>
       <c r="H210" s="3" t="inlineStr">
         <is>
-          <t>checkInstall</t>
+          <t>check_session</t>
         </is>
       </c>
     </row>
@@ -8782,7 +8782,7 @@
       </c>
       <c r="F211" s="5" t="inlineStr">
         <is>
-          <t>/auth/checkRemote/{user}</t>
+          <t>/auth/checkInstall</t>
         </is>
       </c>
       <c r="G211" s="5" t="inlineStr">
@@ -8792,7 +8792,7 @@
       </c>
       <c r="H211" s="3" t="inlineStr">
         <is>
-          <t>check_remoteUser</t>
+          <t>checkInstall</t>
         </is>
       </c>
     </row>
@@ -8812,70 +8812,71 @@
       </c>
       <c r="D212" s="3" t="inlineStr">
         <is>
+          <t>store/auth.js</t>
+        </is>
+      </c>
+      <c r="E212" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="F212" s="5" t="inlineStr">
+        <is>
+          <t>/auth/checkRemote/{user}</t>
+        </is>
+      </c>
+      <c r="G212" s="5" t="inlineStr">
+        <is>
+          <t>routes/auth.py</t>
+        </is>
+      </c>
+      <c r="H212" s="3" t="inlineStr">
+        <is>
+          <t>check_remoteUser</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="3" t="n">
+        <v>204</v>
+      </c>
+      <c r="B213" s="3" t="inlineStr">
+        <is>
+          <t>/trend/:channel</t>
+        </is>
+      </c>
+      <c r="C213" s="3" t="inlineStr">
+        <is>
+          <t>pages/main/Trend.vue</t>
+        </is>
+      </c>
+      <c r="D213" s="3" t="inlineStr">
+        <is>
           <t>store/setup.js</t>
         </is>
       </c>
-      <c r="E212" s="4" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="F212" s="5" t="inlineStr">
+      <c r="E213" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="F213" s="5" t="inlineStr">
         <is>
           <t>/setting/checkSettingFile</t>
         </is>
       </c>
-      <c r="G212" s="5" t="inlineStr">
+      <c r="G213" s="5" t="inlineStr">
         <is>
           <t>routes/setting.py</t>
         </is>
       </c>
-      <c r="H212" s="3" t="inlineStr">
+      <c r="H213" s="3" t="inlineStr">
         <is>
           <t>check_setupfile</t>
         </is>
       </c>
     </row>
-    <row r="214">
-      <c r="A214" s="3" t="n">
-        <v>204</v>
-      </c>
-      <c r="B214" s="3" t="inlineStr">
-        <is>
-          <t>/settings/:mode/:channel</t>
-        </is>
-      </c>
-      <c r="C214" s="3" t="inlineStr">
-        <is>
-          <t>pages/main/SettingNew.vue</t>
-        </is>
-      </c>
-      <c r="D214" s="3" t="inlineStr">
-        <is>
-          <t>components/OnboardingModal2.vue</t>
-        </is>
-      </c>
-      <c r="E214" s="4" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="F214" s="5" t="inlineStr">
-        <is>
-          <t>/setting/apply</t>
-        </is>
-      </c>
-      <c r="G214" s="5" t="inlineStr">
-        <is>
-          <t>routes/setting.py</t>
-        </is>
-      </c>
-      <c r="H214" s="3" t="inlineStr">
-        <is>
-          <t>apply</t>
-        </is>
-      </c>
-    </row>
+    <row r="214"/>
     <row r="215">
       <c r="A215" s="3" t="n">
         <v>205</v>
@@ -8902,7 +8903,7 @@
       </c>
       <c r="F215" s="5" t="inlineStr">
         <is>
-          <t>/setting/checkCommision/{asset}</t>
+          <t>/setting/apply</t>
         </is>
       </c>
       <c r="G215" s="5" t="inlineStr">
@@ -8912,7 +8913,7 @@
       </c>
       <c r="H215" s="3" t="inlineStr">
         <is>
-          <t>check_comm</t>
+          <t>apply</t>
         </is>
       </c>
     </row>
@@ -8942,7 +8943,7 @@
       </c>
       <c r="F216" s="5" t="inlineStr">
         <is>
-          <t>/setting/getSetting</t>
+          <t>/setting/checkCommision/{asset}</t>
         </is>
       </c>
       <c r="G216" s="5" t="inlineStr">
@@ -8952,7 +8953,7 @@
       </c>
       <c r="H216" s="3" t="inlineStr">
         <is>
-          <t>get_setting</t>
+          <t>check_comm</t>
         </is>
       </c>
     </row>
@@ -8982,7 +8983,7 @@
       </c>
       <c r="F217" s="5" t="inlineStr">
         <is>
-          <t>/setting/testwave/{asset}</t>
+          <t>/setting/getSetting</t>
         </is>
       </c>
       <c r="G217" s="5" t="inlineStr">
@@ -8992,7 +8993,7 @@
       </c>
       <c r="H217" s="3" t="inlineStr">
         <is>
-          <t>test_wave</t>
+          <t>get_setting</t>
         </is>
       </c>
     </row>
@@ -9022,7 +9023,7 @@
       </c>
       <c r="F218" s="5" t="inlineStr">
         <is>
-          <t>/setting/test/{channel}/{asset}</t>
+          <t>/setting/testwave/{asset}</t>
         </is>
       </c>
       <c r="G218" s="5" t="inlineStr">
@@ -9032,7 +9033,7 @@
       </c>
       <c r="H218" s="3" t="inlineStr">
         <is>
-          <t>test_asset</t>
+          <t>test_wave</t>
         </is>
       </c>
     </row>
@@ -9062,7 +9063,7 @@
       </c>
       <c r="F219" s="5" t="inlineStr">
         <is>
-          <t>/setting/trigger</t>
+          <t>/setting/test/{channel}/{asset}</t>
         </is>
       </c>
       <c r="G219" s="5" t="inlineStr">
@@ -9072,7 +9073,7 @@
       </c>
       <c r="H219" s="3" t="inlineStr">
         <is>
-          <t>trigger_waveform</t>
+          <t>test_asset</t>
         </is>
       </c>
     </row>
@@ -9102,7 +9103,7 @@
       </c>
       <c r="F220" s="5" t="inlineStr">
         <is>
-          <t>/setting/restartdevice</t>
+          <t>/setting/trigger</t>
         </is>
       </c>
       <c r="G220" s="5" t="inlineStr">
@@ -9112,7 +9113,7 @@
       </c>
       <c r="H220" s="3" t="inlineStr">
         <is>
-          <t>restartdevice</t>
+          <t>trigger_waveform</t>
         </is>
       </c>
     </row>
@@ -9142,7 +9143,7 @@
       </c>
       <c r="F221" s="5" t="inlineStr">
         <is>
-          <t>/setting/restartCore</t>
+          <t>/setting/restartdevice</t>
         </is>
       </c>
       <c r="G221" s="5" t="inlineStr">
@@ -9152,7 +9153,7 @@
       </c>
       <c r="H221" s="3" t="inlineStr">
         <is>
-          <t>restart_core</t>
+          <t>restartdevice</t>
         </is>
       </c>
     </row>
@@ -9172,17 +9173,17 @@
       </c>
       <c r="D222" s="3" t="inlineStr">
         <is>
-          <t>components/SaveProgressModal.vue</t>
+          <t>components/OnboardingModal2.vue</t>
         </is>
       </c>
       <c r="E222" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="F222" s="5" t="inlineStr">
         <is>
-          <t>/setting/setAssetConfig/{asset}</t>
+          <t>/setting/restartCore</t>
         </is>
       </c>
       <c r="G222" s="5" t="inlineStr">
@@ -9192,7 +9193,7 @@
       </c>
       <c r="H222" s="3" t="inlineStr">
         <is>
-          <t>set_assetconfig</t>
+          <t>restart_core</t>
         </is>
       </c>
     </row>
@@ -9222,7 +9223,7 @@
       </c>
       <c r="F223" s="5" t="inlineStr">
         <is>
-          <t>/setting/checkAssetConfig/{asset}</t>
+          <t>/setting/setAssetConfig/{asset}</t>
         </is>
       </c>
       <c r="G223" s="5" t="inlineStr">
@@ -9232,7 +9233,7 @@
       </c>
       <c r="H223" s="3" t="inlineStr">
         <is>
-          <t>check_assetconfig</t>
+          <t>set_assetconfig</t>
         </is>
       </c>
     </row>
@@ -9262,7 +9263,7 @@
       </c>
       <c r="F224" s="5" t="inlineStr">
         <is>
-          <t>/setting/setAssetParams/{asset}</t>
+          <t>/setting/checkAssetConfig/{asset}</t>
         </is>
       </c>
       <c r="G224" s="5" t="inlineStr">
@@ -9272,7 +9273,7 @@
       </c>
       <c r="H224" s="3" t="inlineStr">
         <is>
-          <t>set_assetParams</t>
+          <t>check_assetconfig</t>
         </is>
       </c>
     </row>
@@ -9302,7 +9303,7 @@
       </c>
       <c r="F225" s="5" t="inlineStr">
         <is>
-          <t>/setting/setDiagnosisSetting</t>
+          <t>/setting/setAssetParams/{asset}</t>
         </is>
       </c>
       <c r="G225" s="5" t="inlineStr">
@@ -9312,7 +9313,7 @@
       </c>
       <c r="H225" s="3" t="inlineStr">
         <is>
-          <t>set_diagnosissetting</t>
+          <t>set_assetParams</t>
         </is>
       </c>
     </row>
@@ -9342,7 +9343,7 @@
       </c>
       <c r="F226" s="5" t="inlineStr">
         <is>
-          <t>/setting/setDiagnosisProfile</t>
+          <t>/setting/setDiagnosisSetting</t>
         </is>
       </c>
       <c r="G226" s="5" t="inlineStr">
@@ -9352,7 +9353,7 @@
       </c>
       <c r="H226" s="3" t="inlineStr">
         <is>
-          <t>set_diagnosisprofile</t>
+          <t>set_diagnosissetting</t>
         </is>
       </c>
     </row>
@@ -9382,7 +9383,7 @@
       </c>
       <c r="F227" s="5" t="inlineStr">
         <is>
-          <t>/setting/savefileNew</t>
+          <t>/setting/setDiagnosisProfile</t>
         </is>
       </c>
       <c r="G227" s="5" t="inlineStr">
@@ -9392,7 +9393,7 @@
       </c>
       <c r="H227" s="3" t="inlineStr">
         <is>
-          <t>saveSetting2</t>
+          <t>set_diagnosisprofile</t>
         </is>
       </c>
     </row>
@@ -9417,12 +9418,12 @@
       </c>
       <c r="E228" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="F228" s="5" t="inlineStr">
         <is>
-          <t>/setting/getDiagnosisSetting</t>
+          <t>/setting/savefileNew</t>
         </is>
       </c>
       <c r="G228" s="5" t="inlineStr">
@@ -9432,7 +9433,7 @@
       </c>
       <c r="H228" s="3" t="inlineStr">
         <is>
-          <t>get_diagnosissetting</t>
+          <t>saveSetting2</t>
         </is>
       </c>
     </row>
@@ -9452,7 +9453,7 @@
       </c>
       <c r="D229" s="3" t="inlineStr">
         <is>
-          <t>pages/common/Header.vue</t>
+          <t>components/SaveProgressModal.vue</t>
         </is>
       </c>
       <c r="E229" s="4" t="inlineStr">
@@ -9462,17 +9463,17 @@
       </c>
       <c r="F229" s="5" t="inlineStr">
         <is>
-          <t>/api/getSystemStatus</t>
+          <t>/setting/getDiagnosisSetting</t>
         </is>
       </c>
       <c r="G229" s="5" t="inlineStr">
         <is>
-          <t>routes/api.py</t>
+          <t>routes/setting.py</t>
         </is>
       </c>
       <c r="H229" s="3" t="inlineStr">
         <is>
-          <t>get_service</t>
+          <t>get_diagnosissetting</t>
         </is>
       </c>
     </row>
@@ -9492,7 +9493,7 @@
       </c>
       <c r="D230" s="3" t="inlineStr">
         <is>
-          <t>pages/common/SearchModal.vue</t>
+          <t>pages/common/Header.vue</t>
         </is>
       </c>
       <c r="E230" s="4" t="inlineStr">
@@ -9502,17 +9503,17 @@
       </c>
       <c r="F230" s="5" t="inlineStr">
         <is>
-          <t>/setting/checkBearing</t>
+          <t>/api/getSystemStatus</t>
         </is>
       </c>
       <c r="G230" s="5" t="inlineStr">
         <is>
-          <t>routes/setting.py</t>
+          <t>routes/api.py</t>
         </is>
       </c>
       <c r="H230" s="3" t="inlineStr">
         <is>
-          <t>load_bearings_from_db</t>
+          <t>get_service</t>
         </is>
       </c>
     </row>
@@ -9532,27 +9533,27 @@
       </c>
       <c r="D231" s="3" t="inlineStr">
         <is>
-          <t>pages/header/DropdownClock.vue</t>
+          <t>pages/common/SearchModal.vue</t>
         </is>
       </c>
       <c r="E231" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="F231" s="5" t="inlineStr">
         <is>
-          <t>/config/checktime</t>
+          <t>/setting/checkBearing</t>
         </is>
       </c>
       <c r="G231" s="5" t="inlineStr">
         <is>
-          <t>routes/config.py</t>
+          <t>routes/setting.py</t>
         </is>
       </c>
       <c r="H231" s="3" t="inlineStr">
         <is>
-          <t>check_device_time</t>
+          <t>load_bearings_from_db</t>
         </is>
       </c>
     </row>
@@ -9582,17 +9583,17 @@
       </c>
       <c r="F232" s="5" t="inlineStr">
         <is>
-          <t>/setting/setSystemTime</t>
+          <t>/config/checktime</t>
         </is>
       </c>
       <c r="G232" s="5" t="inlineStr">
         <is>
-          <t>routes/setting.py</t>
+          <t>routes/config.py</t>
         </is>
       </c>
       <c r="H232" s="3" t="inlineStr">
         <is>
-          <t>setup_system_time</t>
+          <t>check_device_time</t>
         </is>
       </c>
     </row>
@@ -9612,27 +9613,27 @@
       </c>
       <c r="D233" s="3" t="inlineStr">
         <is>
-          <t>pages/header/DropdownHelp.vue</t>
+          <t>pages/header/DropdownClock.vue</t>
         </is>
       </c>
       <c r="E233" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="F233" s="5" t="inlineStr">
         <is>
-          <t>/api/download/{mode}/{lang}</t>
+          <t>/setting/setSystemTime</t>
         </is>
       </c>
       <c r="G233" s="5" t="inlineStr">
         <is>
-          <t>routes/api.py</t>
+          <t>routes/setting.py</t>
         </is>
       </c>
       <c r="H233" s="3" t="inlineStr">
         <is>
-          <t>get_deviceDoc</t>
+          <t>setup_system_time</t>
         </is>
       </c>
     </row>
@@ -9652,7 +9653,7 @@
       </c>
       <c r="D234" s="3" t="inlineStr">
         <is>
-          <t>pages/main/SettingNew.vue</t>
+          <t>pages/header/DropdownHelp.vue</t>
         </is>
       </c>
       <c r="E234" s="4" t="inlineStr">
@@ -9662,17 +9663,17 @@
       </c>
       <c r="F234" s="5" t="inlineStr">
         <is>
-          <t>/setting/checkSmart</t>
+          <t>/api/download/{mode}/{lang}</t>
         </is>
       </c>
       <c r="G234" s="5" t="inlineStr">
         <is>
-          <t>routes/setting.py</t>
+          <t>routes/api.py</t>
         </is>
       </c>
       <c r="H234" s="3" t="inlineStr">
         <is>
-          <t>sendSmartStatus</t>
+          <t>get_deviceDoc</t>
         </is>
       </c>
     </row>
@@ -9702,7 +9703,7 @@
       </c>
       <c r="F235" s="5" t="inlineStr">
         <is>
-          <t>/setting/manageSmart/{mode}</t>
+          <t>/setting/checkSmart</t>
         </is>
       </c>
       <c r="G235" s="5" t="inlineStr">
@@ -9712,7 +9713,7 @@
       </c>
       <c r="H235" s="3" t="inlineStr">
         <is>
-          <t>manage_smart</t>
+          <t>sendSmartStatus</t>
         </is>
       </c>
     </row>
@@ -9742,7 +9743,7 @@
       </c>
       <c r="F236" s="5" t="inlineStr">
         <is>
-          <t>/setting/restartasset</t>
+          <t>/setting/manageSmart/{mode}</t>
         </is>
       </c>
       <c r="G236" s="5" t="inlineStr">
@@ -9752,7 +9753,7 @@
       </c>
       <c r="H236" s="3" t="inlineStr">
         <is>
-          <t>restartasset</t>
+          <t>manage_smart</t>
         </is>
       </c>
     </row>
@@ -9782,7 +9783,7 @@
       </c>
       <c r="F237" s="5" t="inlineStr">
         <is>
-          <t>/setting/SysService/{cmd}/{item}</t>
+          <t>/setting/restartasset</t>
         </is>
       </c>
       <c r="G237" s="5" t="inlineStr">
@@ -9792,7 +9793,7 @@
       </c>
       <c r="H237" s="3" t="inlineStr">
         <is>
-          <t>control_service</t>
+          <t>restartasset</t>
         </is>
       </c>
     </row>
@@ -9822,7 +9823,7 @@
       </c>
       <c r="F238" s="5" t="inlineStr">
         <is>
-          <t>/setting/applyNetwork</t>
+          <t>/setting/SysService/{cmd}/{item}</t>
         </is>
       </c>
       <c r="G238" s="5" t="inlineStr">
@@ -9832,7 +9833,7 @@
       </c>
       <c r="H238" s="3" t="inlineStr">
         <is>
-          <t>apply_network</t>
+          <t>control_service</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9863,7 @@
       </c>
       <c r="F239" s="5" t="inlineStr">
         <is>
-          <t>/setting/checkMQTT</t>
+          <t>/setting/applyNetwork</t>
         </is>
       </c>
       <c r="G239" s="5" t="inlineStr">
@@ -9872,7 +9873,7 @@
       </c>
       <c r="H239" s="3" t="inlineStr">
         <is>
-          <t>check_mqtt</t>
+          <t>apply_network</t>
         </is>
       </c>
     </row>
@@ -9902,7 +9903,7 @@
       </c>
       <c r="F240" s="5" t="inlineStr">
         <is>
-          <t>/setting/checkFRP</t>
+          <t>/setting/checkMQTT</t>
         </is>
       </c>
       <c r="G240" s="5" t="inlineStr">
@@ -9912,7 +9913,7 @@
       </c>
       <c r="H240" s="3" t="inlineStr">
         <is>
-          <t>check_frp</t>
+          <t>check_mqtt</t>
         </is>
       </c>
     </row>
@@ -9942,7 +9943,7 @@
       </c>
       <c r="F241" s="5" t="inlineStr">
         <is>
-          <t>/setting/getSettingData/{channel}</t>
+          <t>/setting/checkFRP</t>
         </is>
       </c>
       <c r="G241" s="5" t="inlineStr">
@@ -9952,7 +9953,7 @@
       </c>
       <c r="H241" s="3" t="inlineStr">
         <is>
-          <t>getDatafromSetting</t>
+          <t>check_frp</t>
         </is>
       </c>
     </row>
@@ -9982,7 +9983,7 @@
       </c>
       <c r="F242" s="5" t="inlineStr">
         <is>
-          <t>/setting/getDiagnosisSetting</t>
+          <t>/setting/getSettingData/{channel}</t>
         </is>
       </c>
       <c r="G242" s="5" t="inlineStr">
@@ -9992,7 +9993,7 @@
       </c>
       <c r="H242" s="3" t="inlineStr">
         <is>
-          <t>get_diagnosissetting</t>
+          <t>getDatafromSetting</t>
         </is>
       </c>
     </row>
@@ -10022,7 +10023,7 @@
       </c>
       <c r="F243" s="5" t="inlineStr">
         <is>
-          <t>/setting/getDiagnosisProfile</t>
+          <t>/setting/getDiagnosisSetting</t>
         </is>
       </c>
       <c r="G243" s="5" t="inlineStr">
@@ -10032,7 +10033,7 @@
       </c>
       <c r="H243" s="3" t="inlineStr">
         <is>
-          <t>get_diagnosisprofile</t>
+          <t>get_diagnosissetting</t>
         </is>
       </c>
     </row>
@@ -10062,7 +10063,7 @@
       </c>
       <c r="F244" s="5" t="inlineStr">
         <is>
-          <t>/setting/getSetting</t>
+          <t>/setting/getDiagnosisProfile</t>
         </is>
       </c>
       <c r="G244" s="5" t="inlineStr">
@@ -10072,7 +10073,7 @@
       </c>
       <c r="H244" s="3" t="inlineStr">
         <is>
-          <t>get_setting</t>
+          <t>get_diagnosisprofile</t>
         </is>
       </c>
     </row>
@@ -10102,7 +10103,7 @@
       </c>
       <c r="F245" s="5" t="inlineStr">
         <is>
-          <t>/setting/Reset</t>
+          <t>/setting/getSetting</t>
         </is>
       </c>
       <c r="G245" s="5" t="inlineStr">
@@ -10112,7 +10113,7 @@
       </c>
       <c r="H245" s="3" t="inlineStr">
         <is>
-          <t>reset</t>
+          <t>get_setting</t>
         </is>
       </c>
     </row>
@@ -10132,7 +10133,7 @@
       </c>
       <c r="D246" s="3" t="inlineStr">
         <is>
-          <t>partials/inners/setting/APIPanel.vue</t>
+          <t>pages/main/SettingNew.vue</t>
         </is>
       </c>
       <c r="E246" s="4" t="inlineStr">
@@ -10142,17 +10143,17 @@
       </c>
       <c r="F246" s="5" t="inlineStr">
         <is>
-          <t>/auth/getAPIUsers</t>
+          <t>/setting/Reset</t>
         </is>
       </c>
       <c r="G246" s="5" t="inlineStr">
         <is>
-          <t>routes/auth.py</t>
+          <t>routes/setting.py</t>
         </is>
       </c>
       <c r="H246" s="3" t="inlineStr">
         <is>
-          <t>get_users</t>
+          <t>reset</t>
         </is>
       </c>
     </row>
@@ -10182,7 +10183,7 @@
       </c>
       <c r="F247" s="5" t="inlineStr">
         <is>
-          <t>/auth/joinAPI/{role}</t>
+          <t>/auth/getAPIUsers</t>
         </is>
       </c>
       <c r="G247" s="5" t="inlineStr">
@@ -10192,7 +10193,7 @@
       </c>
       <c r="H247" s="3" t="inlineStr">
         <is>
-          <t>join_default</t>
+          <t>get_users</t>
         </is>
       </c>
     </row>
@@ -10222,7 +10223,7 @@
       </c>
       <c r="F248" s="5" t="inlineStr">
         <is>
-          <t>/auth/removeAPI/{role}</t>
+          <t>/auth/joinAPI/{role}</t>
         </is>
       </c>
       <c r="G248" s="5" t="inlineStr">
@@ -10232,7 +10233,7 @@
       </c>
       <c r="H248" s="3" t="inlineStr">
         <is>
-          <t>remove_default</t>
+          <t>join_default</t>
         </is>
       </c>
     </row>
@@ -10252,7 +10253,7 @@
       </c>
       <c r="D249" s="3" t="inlineStr">
         <is>
-          <t>partials/inners/setting/AccountPanel.vue</t>
+          <t>partials/inners/setting/APIPanel.vue</t>
         </is>
       </c>
       <c r="E249" s="4" t="inlineStr">
@@ -10262,7 +10263,7 @@
       </c>
       <c r="F249" s="5" t="inlineStr">
         <is>
-          <t>/auth/getUser</t>
+          <t>/auth/removeAPI/{role}</t>
         </is>
       </c>
       <c r="G249" s="5" t="inlineStr">
@@ -10272,7 +10273,7 @@
       </c>
       <c r="H249" s="3" t="inlineStr">
         <is>
-          <t>getUser</t>
+          <t>remove_default</t>
         </is>
       </c>
     </row>
@@ -10297,12 +10298,12 @@
       </c>
       <c r="E250" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="F250" s="5" t="inlineStr">
         <is>
-          <t>/auth/updateProfile</t>
+          <t>/auth/getUser</t>
         </is>
       </c>
       <c r="G250" s="5" t="inlineStr">
@@ -10312,7 +10313,7 @@
       </c>
       <c r="H250" s="3" t="inlineStr">
         <is>
-          <t>updateProfile</t>
+          <t>getUser</t>
         </is>
       </c>
     </row>
@@ -10332,27 +10333,27 @@
       </c>
       <c r="D251" s="3" t="inlineStr">
         <is>
-          <t>partials/inners/setting/AssetCard.vue</t>
+          <t>partials/inners/setting/AccountPanel.vue</t>
         </is>
       </c>
       <c r="E251" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="F251" s="5" t="inlineStr">
         <is>
-          <t>/setting/getAssetList</t>
+          <t>/auth/updateProfile</t>
         </is>
       </c>
       <c r="G251" s="5" t="inlineStr">
         <is>
-          <t>routes/setting.py</t>
+          <t>routes/auth.py</t>
         </is>
       </c>
       <c r="H251" s="3" t="inlineStr">
         <is>
-          <t>get_assetlist</t>
+          <t>updateProfile</t>
         </is>
       </c>
     </row>
@@ -10382,7 +10383,7 @@
       </c>
       <c r="F252" s="5" t="inlineStr">
         <is>
-          <t>/setting/getAssetTypes</t>
+          <t>/setting/getAssetList</t>
         </is>
       </c>
       <c r="G252" s="5" t="inlineStr">
@@ -10392,7 +10393,7 @@
       </c>
       <c r="H252" s="3" t="inlineStr">
         <is>
-          <t>get_assetTypes</t>
+          <t>get_assetlist</t>
         </is>
       </c>
     </row>
@@ -10422,7 +10423,7 @@
       </c>
       <c r="F253" s="5" t="inlineStr">
         <is>
-          <t>/setting/unregisterAsset/{channel}/{asset}</t>
+          <t>/setting/getAssetTypes</t>
         </is>
       </c>
       <c r="G253" s="5" t="inlineStr">
@@ -10432,7 +10433,7 @@
       </c>
       <c r="H253" s="3" t="inlineStr">
         <is>
-          <t>unreg_Asset</t>
+          <t>get_assetTypes</t>
         </is>
       </c>
     </row>
@@ -10462,17 +10463,17 @@
       </c>
       <c r="F254" s="5" t="inlineStr">
         <is>
-          <t>/api/relearn/{asset}</t>
+          <t>/setting/unregisterAsset/{channel}/{asset}</t>
         </is>
       </c>
       <c r="G254" s="5" t="inlineStr">
         <is>
-          <t>routes/api.py</t>
+          <t>routes/setting.py</t>
         </is>
       </c>
       <c r="H254" s="3" t="inlineStr">
         <is>
-          <t>relearn_asset</t>
+          <t>unreg_Asset</t>
         </is>
       </c>
     </row>
@@ -10502,17 +10503,17 @@
       </c>
       <c r="F255" s="5" t="inlineStr">
         <is>
-          <t>/setting/registerAsset/{channel}/{assetName}/{assetType}</t>
+          <t>/api/relearn/{asset}</t>
         </is>
       </c>
       <c r="G255" s="5" t="inlineStr">
         <is>
-          <t>routes/setting.py</t>
+          <t>routes/api.py</t>
         </is>
       </c>
       <c r="H255" s="3" t="inlineStr">
         <is>
-          <t>reg_Asset</t>
+          <t>relearn_asset</t>
         </is>
       </c>
     </row>
@@ -10537,12 +10538,12 @@
       </c>
       <c r="E256" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="F256" s="5" t="inlineStr">
         <is>
-          <t>/setting/createAsset</t>
+          <t>/setting/registerAsset/{channel}/{assetName}/{assetType}</t>
         </is>
       </c>
       <c r="G256" s="5" t="inlineStr">
@@ -10552,7 +10553,7 @@
       </c>
       <c r="H256" s="3" t="inlineStr">
         <is>
-          <t>createAsset</t>
+          <t>reg_Asset</t>
         </is>
       </c>
     </row>
@@ -10582,7 +10583,7 @@
       </c>
       <c r="F257" s="5" t="inlineStr">
         <is>
-          <t>/setting/modifyAsset</t>
+          <t>/setting/createAsset</t>
         </is>
       </c>
       <c r="G257" s="5" t="inlineStr">
@@ -10592,7 +10593,7 @@
       </c>
       <c r="H257" s="3" t="inlineStr">
         <is>
-          <t>modifyAsset</t>
+          <t>createAsset</t>
         </is>
       </c>
     </row>
@@ -10617,12 +10618,12 @@
       </c>
       <c r="E258" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="F258" s="5" t="inlineStr">
         <is>
-          <t>/setting/deleteAsset/{asset}</t>
+          <t>/setting/modifyAsset</t>
         </is>
       </c>
       <c r="G258" s="5" t="inlineStr">
@@ -10632,7 +10633,7 @@
       </c>
       <c r="H258" s="3" t="inlineStr">
         <is>
-          <t>deleteAsset</t>
+          <t>modifyAsset</t>
         </is>
       </c>
     </row>
@@ -10652,7 +10653,7 @@
       </c>
       <c r="D259" s="3" t="inlineStr">
         <is>
-          <t>partials/inners/setting/BillingPanel.vue</t>
+          <t>partials/inners/setting/AssetCard.vue</t>
         </is>
       </c>
       <c r="E259" s="4" t="inlineStr">
@@ -10662,17 +10663,17 @@
       </c>
       <c r="F259" s="5" t="inlineStr">
         <is>
-          <t>/auth/getUserList</t>
+          <t>/setting/deleteAsset/{asset}</t>
         </is>
       </c>
       <c r="G259" s="5" t="inlineStr">
         <is>
-          <t>routes/auth.py</t>
+          <t>routes/setting.py</t>
         </is>
       </c>
       <c r="H259" s="3" t="inlineStr">
         <is>
-          <t>get_Userlist</t>
+          <t>deleteAsset</t>
         </is>
       </c>
     </row>
@@ -10697,12 +10698,12 @@
       </c>
       <c r="E260" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="F260" s="5" t="inlineStr">
         <is>
-          <t>/auth/join</t>
+          <t>/auth/getUserList</t>
         </is>
       </c>
       <c r="G260" s="5" t="inlineStr">
@@ -10712,7 +10713,7 @@
       </c>
       <c r="H260" s="3" t="inlineStr">
         <is>
-          <t>join</t>
+          <t>get_Userlist</t>
         </is>
       </c>
     </row>
@@ -10737,12 +10738,12 @@
       </c>
       <c r="E261" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="F261" s="5" t="inlineStr">
         <is>
-          <t>/auth/removeUser/{username}</t>
+          <t>/auth/join</t>
         </is>
       </c>
       <c r="G261" s="5" t="inlineStr">
@@ -10752,7 +10753,7 @@
       </c>
       <c r="H261" s="3" t="inlineStr">
         <is>
-          <t>removeUser</t>
+          <t>join</t>
         </is>
       </c>
     </row>
@@ -10782,7 +10783,7 @@
       </c>
       <c r="F262" s="5" t="inlineStr">
         <is>
-          <t>/auth/saveUser/{account}/{role}</t>
+          <t>/auth/removeUser/{username}</t>
         </is>
       </c>
       <c r="G262" s="5" t="inlineStr">
@@ -10792,7 +10793,7 @@
       </c>
       <c r="H262" s="3" t="inlineStr">
         <is>
-          <t>updateRole</t>
+          <t>removeUser</t>
         </is>
       </c>
     </row>
@@ -10812,7 +10813,7 @@
       </c>
       <c r="D263" s="3" t="inlineStr">
         <is>
-          <t>partials/inners/setting/ChannelPanel.vue</t>
+          <t>partials/inners/setting/BillingPanel.vue</t>
         </is>
       </c>
       <c r="E263" s="4" t="inlineStr">
@@ -10822,17 +10823,17 @@
       </c>
       <c r="F263" s="5" t="inlineStr">
         <is>
-          <t>/setting/getAssetConfig/{asset}</t>
+          <t>/auth/saveUser/{account}/{role}</t>
         </is>
       </c>
       <c r="G263" s="5" t="inlineStr">
         <is>
-          <t>routes/setting.py</t>
+          <t>routes/auth.py</t>
         </is>
       </c>
       <c r="H263" s="3" t="inlineStr">
         <is>
-          <t>get_assetconfig</t>
+          <t>updateRole</t>
         </is>
       </c>
     </row>
@@ -10862,7 +10863,7 @@
       </c>
       <c r="F264" s="5" t="inlineStr">
         <is>
-          <t>/setting/getAssetParams/{asset}</t>
+          <t>/setting/getAssetConfig/{asset}</t>
         </is>
       </c>
       <c r="G264" s="5" t="inlineStr">
@@ -10872,7 +10873,7 @@
       </c>
       <c r="H264" s="3" t="inlineStr">
         <is>
-          <t>get_assetParams</t>
+          <t>get_assetconfig</t>
         </is>
       </c>
     </row>
@@ -10897,12 +10898,12 @@
       </c>
       <c r="E265" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="F265" s="5" t="inlineStr">
         <is>
-          <t>/setting/setAssetParams/{asset}</t>
+          <t>/setting/getAssetParams/{asset}</t>
         </is>
       </c>
       <c r="G265" s="5" t="inlineStr">
@@ -10912,7 +10913,7 @@
       </c>
       <c r="H265" s="3" t="inlineStr">
         <is>
-          <t>set_assetParams</t>
+          <t>get_assetParams</t>
         </is>
       </c>
     </row>
@@ -10942,7 +10943,7 @@
       </c>
       <c r="F266" s="5" t="inlineStr">
         <is>
-          <t>/setting/setAssetConfig/{asset}</t>
+          <t>/setting/setAssetParams/{asset}</t>
         </is>
       </c>
       <c r="G266" s="5" t="inlineStr">
@@ -10952,7 +10953,7 @@
       </c>
       <c r="H266" s="3" t="inlineStr">
         <is>
-          <t>set_assetconfig</t>
+          <t>set_assetParams</t>
         </is>
       </c>
     </row>
@@ -10982,7 +10983,7 @@
       </c>
       <c r="F267" s="5" t="inlineStr">
         <is>
-          <t>/setting/checkAssetConfig/{asset}</t>
+          <t>/setting/setAssetConfig/{asset}</t>
         </is>
       </c>
       <c r="G267" s="5" t="inlineStr">
@@ -10992,7 +10993,7 @@
       </c>
       <c r="H267" s="3" t="inlineStr">
         <is>
-          <t>check_assetconfig</t>
+          <t>set_assetconfig</t>
         </is>
       </c>
     </row>
@@ -11017,12 +11018,12 @@
       </c>
       <c r="E268" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="F268" s="5" t="inlineStr">
         <is>
-          <t>/setting/restartasset</t>
+          <t>/setting/checkAssetConfig/{asset}</t>
         </is>
       </c>
       <c r="G268" s="5" t="inlineStr">
@@ -11032,7 +11033,7 @@
       </c>
       <c r="H268" s="3" t="inlineStr">
         <is>
-          <t>restartasset</t>
+          <t>check_assetconfig</t>
         </is>
       </c>
     </row>
@@ -11052,7 +11053,7 @@
       </c>
       <c r="D269" s="3" t="inlineStr">
         <is>
-          <t>partials/inners/setting/CommandItem.vue</t>
+          <t>partials/inners/setting/ChannelPanel.vue</t>
         </is>
       </c>
       <c r="E269" s="4" t="inlineStr">
@@ -11062,7 +11063,7 @@
       </c>
       <c r="F269" s="5" t="inlineStr">
         <is>
-          <t>/setting/SysService/{cmd}/{item}</t>
+          <t>/setting/restartasset</t>
         </is>
       </c>
       <c r="G269" s="5" t="inlineStr">
@@ -11072,7 +11073,7 @@
       </c>
       <c r="H269" s="3" t="inlineStr">
         <is>
-          <t>control_service</t>
+          <t>restartasset</t>
         </is>
       </c>
     </row>
@@ -11097,12 +11098,12 @@
       </c>
       <c r="E270" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="F270" s="5" t="inlineStr">
         <is>
-          <t>/setting/command</t>
+          <t>/setting/SysService/{cmd}/{item}</t>
         </is>
       </c>
       <c r="G270" s="5" t="inlineStr">
@@ -11112,7 +11113,7 @@
       </c>
       <c r="H270" s="3" t="inlineStr">
         <is>
-          <t>push_command_left</t>
+          <t>control_service</t>
         </is>
       </c>
     </row>
@@ -11137,22 +11138,22 @@
       </c>
       <c r="E271" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="F271" s="5" t="inlineStr">
         <is>
-          <t>/auth/checkDBMS</t>
+          <t>/setting/command</t>
         </is>
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>routes/auth.py</t>
+          <t>routes/setting.py</t>
         </is>
       </c>
       <c r="H271" s="3" t="inlineStr">
         <is>
-          <t>check_Db</t>
+          <t>push_command_left</t>
         </is>
       </c>
     </row>
@@ -11182,17 +11183,17 @@
       </c>
       <c r="F272" s="5" t="inlineStr">
         <is>
-          <t>/setting/initDB</t>
+          <t>/auth/checkDBMS</t>
         </is>
       </c>
       <c r="G272" s="5" t="inlineStr">
         <is>
-          <t>routes/setting.py</t>
+          <t>routes/auth.py</t>
         </is>
       </c>
       <c r="H272" s="3" t="inlineStr">
         <is>
-          <t>initInflux</t>
+          <t>check_Db</t>
         </is>
       </c>
     </row>
@@ -11222,7 +11223,7 @@
       </c>
       <c r="F273" s="5" t="inlineStr">
         <is>
-          <t>/setting/ResetAll</t>
+          <t>/setting/initDB</t>
         </is>
       </c>
       <c r="G273" s="5" t="inlineStr">
@@ -11232,7 +11233,7 @@
       </c>
       <c r="H273" s="3" t="inlineStr">
         <is>
-          <t>resetAll</t>
+          <t>initInflux</t>
         </is>
       </c>
     </row>
@@ -11262,7 +11263,7 @@
       </c>
       <c r="F274" s="5" t="inlineStr">
         <is>
-          <t>/setting/Reset</t>
+          <t>/setting/ResetAll</t>
         </is>
       </c>
       <c r="G274" s="5" t="inlineStr">
@@ -11272,7 +11273,7 @@
       </c>
       <c r="H274" s="3" t="inlineStr">
         <is>
-          <t>reset</t>
+          <t>resetAll</t>
         </is>
       </c>
     </row>
@@ -11297,12 +11298,12 @@
       </c>
       <c r="E275" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="F275" s="5" t="inlineStr">
         <is>
-          <t>/setting/upload</t>
+          <t>/setting/Reset</t>
         </is>
       </c>
       <c r="G275" s="5" t="inlineStr">
@@ -11312,7 +11313,7 @@
       </c>
       <c r="H275" s="3" t="inlineStr">
         <is>
-          <t>upload_file</t>
+          <t>reset</t>
         </is>
       </c>
     </row>
@@ -11337,12 +11338,12 @@
       </c>
       <c r="E276" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="F276" s="5" t="inlineStr">
         <is>
-          <t>/setting/download</t>
+          <t>/setting/upload</t>
         </is>
       </c>
       <c r="G276" s="5" t="inlineStr">
@@ -11352,7 +11353,7 @@
       </c>
       <c r="H276" s="3" t="inlineStr">
         <is>
-          <t>download_setting</t>
+          <t>upload_file</t>
         </is>
       </c>
     </row>
@@ -11377,12 +11378,12 @@
       </c>
       <c r="E277" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="F277" s="5" t="inlineStr">
         <is>
-          <t>/setting/restoreSetting</t>
+          <t>/setting/download</t>
         </is>
       </c>
       <c r="G277" s="5" t="inlineStr">
@@ -11392,7 +11393,7 @@
       </c>
       <c r="H277" s="3" t="inlineStr">
         <is>
-          <t>restore_setting</t>
+          <t>download_setting</t>
         </is>
       </c>
     </row>
@@ -11412,17 +11413,17 @@
       </c>
       <c r="D278" s="3" t="inlineStr">
         <is>
-          <t>partials/inners/setting/CommandPanel.vue</t>
+          <t>partials/inners/setting/CommandItem.vue</t>
         </is>
       </c>
       <c r="E278" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="F278" s="5" t="inlineStr">
         <is>
-          <t>/setting/SysCheck</t>
+          <t>/setting/restoreSetting</t>
         </is>
       </c>
       <c r="G278" s="5" t="inlineStr">
@@ -11432,7 +11433,7 @@
       </c>
       <c r="H278" s="3" t="inlineStr">
         <is>
-          <t>check_sysStatus</t>
+          <t>restore_setting</t>
         </is>
       </c>
     </row>
@@ -11452,7 +11453,7 @@
       </c>
       <c r="D279" s="3" t="inlineStr">
         <is>
-          <t>partials/inners/setting/General_diagnosisCard.vue</t>
+          <t>partials/inners/setting/CommandPanel.vue</t>
         </is>
       </c>
       <c r="E279" s="4" t="inlineStr">
@@ -11462,7 +11463,7 @@
       </c>
       <c r="F279" s="5" t="inlineStr">
         <is>
-          <t>/setting/getDiagnosisProfile</t>
+          <t>/setting/SysCheck</t>
         </is>
       </c>
       <c r="G279" s="5" t="inlineStr">
@@ -11472,7 +11473,7 @@
       </c>
       <c r="H279" s="3" t="inlineStr">
         <is>
-          <t>get_diagnosisprofile</t>
+          <t>check_sysStatus</t>
         </is>
       </c>
     </row>
@@ -11492,7 +11493,7 @@
       </c>
       <c r="D280" s="3" t="inlineStr">
         <is>
-          <t>partials/inners/setting/MQTTCard.vue</t>
+          <t>partials/inners/setting/General_diagnosisCard.vue</t>
         </is>
       </c>
       <c r="E280" s="4" t="inlineStr">
@@ -11502,7 +11503,7 @@
       </c>
       <c r="F280" s="5" t="inlineStr">
         <is>
-          <t>/setting/listCerts</t>
+          <t>/setting/getDiagnosisProfile</t>
         </is>
       </c>
       <c r="G280" s="5" t="inlineStr">
@@ -11512,7 +11513,7 @@
       </c>
       <c r="H280" s="3" t="inlineStr">
         <is>
-          <t>list_certs</t>
+          <t>get_diagnosisprofile</t>
         </is>
       </c>
     </row>
@@ -11537,12 +11538,12 @@
       </c>
       <c r="E281" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="F281" s="5" t="inlineStr">
         <is>
-          <t>/setting/uploadCerts</t>
+          <t>/setting/listCerts</t>
         </is>
       </c>
       <c r="G281" s="5" t="inlineStr">
@@ -11552,7 +11553,7 @@
       </c>
       <c r="H281" s="3" t="inlineStr">
         <is>
-          <t>upload_certs</t>
+          <t>list_certs</t>
         </is>
       </c>
     </row>
@@ -11577,12 +11578,12 @@
       </c>
       <c r="E282" s="4" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="F282" s="5" t="inlineStr">
         <is>
-          <t>/setting/deleteCert/{filename}</t>
+          <t>/setting/uploadCerts</t>
         </is>
       </c>
       <c r="G282" s="5" t="inlineStr">
@@ -11592,7 +11593,7 @@
       </c>
       <c r="H282" s="3" t="inlineStr">
         <is>
-          <t>delete_cert</t>
+          <t>upload_certs</t>
         </is>
       </c>
     </row>
@@ -11612,17 +11613,17 @@
       </c>
       <c r="D283" s="3" t="inlineStr">
         <is>
-          <t>partials/inners/setting/NameplateCard.vue</t>
+          <t>partials/inners/setting/MQTTCard.vue</t>
         </is>
       </c>
       <c r="E283" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="F283" s="5" t="inlineStr">
         <is>
-          <t>/setting/checkBearing</t>
+          <t>/setting/deleteCert/{filename}</t>
         </is>
       </c>
       <c r="G283" s="5" t="inlineStr">
@@ -11632,7 +11633,7 @@
       </c>
       <c r="H283" s="3" t="inlineStr">
         <is>
-          <t>load_bearings_from_db</t>
+          <t>delete_cert</t>
         </is>
       </c>
     </row>
@@ -11657,12 +11658,12 @@
       </c>
       <c r="E284" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="F284" s="5" t="inlineStr">
         <is>
-          <t>/setting/uploadBearing</t>
+          <t>/setting/checkBearing</t>
         </is>
       </c>
       <c r="G284" s="5" t="inlineStr">
@@ -11672,7 +11673,7 @@
       </c>
       <c r="H284" s="3" t="inlineStr">
         <is>
-          <t>upload_bearing_to_db</t>
+          <t>load_bearings_from_db</t>
         </is>
       </c>
     </row>
@@ -11702,7 +11703,7 @@
       </c>
       <c r="F285" s="5" t="inlineStr">
         <is>
-          <t>/setting/setAssetConfig/{asset}</t>
+          <t>/setting/uploadBearing</t>
         </is>
       </c>
       <c r="G285" s="5" t="inlineStr">
@@ -11712,7 +11713,7 @@
       </c>
       <c r="H285" s="3" t="inlineStr">
         <is>
-          <t>set_assetconfig</t>
+          <t>upload_bearing_to_db</t>
         </is>
       </c>
     </row>
@@ -11732,7 +11733,7 @@
       </c>
       <c r="D286" s="3" t="inlineStr">
         <is>
-          <t>partials/inners/setting/PlansPanel.vue</t>
+          <t>partials/inners/setting/NameplateCard.vue</t>
         </is>
       </c>
       <c r="E286" s="4" t="inlineStr">
@@ -11742,7 +11743,7 @@
       </c>
       <c r="F286" s="5" t="inlineStr">
         <is>
-          <t>/setting/setDiagnosisSetting</t>
+          <t>/setting/setAssetConfig/{asset}</t>
         </is>
       </c>
       <c r="G286" s="5" t="inlineStr">
@@ -11752,7 +11753,7 @@
       </c>
       <c r="H286" s="3" t="inlineStr">
         <is>
-          <t>set_diagnosissetting</t>
+          <t>set_assetconfig</t>
         </is>
       </c>
     </row>
@@ -11782,7 +11783,7 @@
       </c>
       <c r="F287" s="5" t="inlineStr">
         <is>
-          <t>/setting/setDiagnosisProfile</t>
+          <t>/setting/setDiagnosisSetting</t>
         </is>
       </c>
       <c r="G287" s="5" t="inlineStr">
@@ -11792,7 +11793,7 @@
       </c>
       <c r="H287" s="3" t="inlineStr">
         <is>
-          <t>set_diagnosisprofile</t>
+          <t>set_diagnosissetting</t>
         </is>
       </c>
     </row>
@@ -11822,7 +11823,7 @@
       </c>
       <c r="F288" s="5" t="inlineStr">
         <is>
-          <t>/setting/upload</t>
+          <t>/setting/setDiagnosisProfile</t>
         </is>
       </c>
       <c r="G288" s="5" t="inlineStr">
@@ -11832,7 +11833,7 @@
       </c>
       <c r="H288" s="3" t="inlineStr">
         <is>
-          <t>upload_file</t>
+          <t>set_diagnosisprofile</t>
         </is>
       </c>
     </row>
@@ -11857,12 +11858,12 @@
       </c>
       <c r="E289" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="F289" s="5" t="inlineStr">
         <is>
-          <t>/setting/getSettingData/{channel}</t>
+          <t>/setting/upload</t>
         </is>
       </c>
       <c r="G289" s="5" t="inlineStr">
@@ -11872,7 +11873,7 @@
       </c>
       <c r="H289" s="3" t="inlineStr">
         <is>
-          <t>getDatafromSetting</t>
+          <t>upload_file</t>
         </is>
       </c>
     </row>
@@ -11892,27 +11893,27 @@
       </c>
       <c r="D290" s="3" t="inlineStr">
         <is>
-          <t>store/auth.js</t>
+          <t>partials/inners/setting/PlansPanel.vue</t>
         </is>
       </c>
       <c r="E290" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="F290" s="5" t="inlineStr">
         <is>
-          <t>/auth/checkLogins</t>
+          <t>/setting/getSettingData/{channel}</t>
         </is>
       </c>
       <c r="G290" s="5" t="inlineStr">
         <is>
-          <t>routes/auth.py</t>
+          <t>routes/setting.py</t>
         </is>
       </c>
       <c r="H290" s="3" t="inlineStr">
         <is>
-          <t>checkLogins</t>
+          <t>getDatafromSetting</t>
         </is>
       </c>
     </row>
@@ -11937,12 +11938,12 @@
       </c>
       <c r="E291" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="F291" s="5" t="inlineStr">
         <is>
-          <t>/auth/logout</t>
+          <t>/auth/checkLogins</t>
         </is>
       </c>
       <c r="G291" s="5" t="inlineStr">
@@ -11952,7 +11953,7 @@
       </c>
       <c r="H291" s="3" t="inlineStr">
         <is>
-          <t>logout</t>
+          <t>checkLogins</t>
         </is>
       </c>
     </row>
@@ -11982,7 +11983,7 @@
       </c>
       <c r="F292" s="5" t="inlineStr">
         <is>
-          <t>/auth/checkSession</t>
+          <t>/auth/logout</t>
         </is>
       </c>
       <c r="G292" s="5" t="inlineStr">
@@ -11992,7 +11993,7 @@
       </c>
       <c r="H292" s="3" t="inlineStr">
         <is>
-          <t>check_session</t>
+          <t>logout</t>
         </is>
       </c>
     </row>
@@ -12022,7 +12023,7 @@
       </c>
       <c r="F293" s="5" t="inlineStr">
         <is>
-          <t>/auth/checkInstall</t>
+          <t>/auth/checkSession</t>
         </is>
       </c>
       <c r="G293" s="5" t="inlineStr">
@@ -12032,7 +12033,7 @@
       </c>
       <c r="H293" s="3" t="inlineStr">
         <is>
-          <t>checkInstall</t>
+          <t>check_session</t>
         </is>
       </c>
     </row>
@@ -12062,7 +12063,7 @@
       </c>
       <c r="F294" s="5" t="inlineStr">
         <is>
-          <t>/auth/checkRemote/{user}</t>
+          <t>/auth/checkInstall</t>
         </is>
       </c>
       <c r="G294" s="5" t="inlineStr">
@@ -12072,7 +12073,7 @@
       </c>
       <c r="H294" s="3" t="inlineStr">
         <is>
-          <t>check_remoteUser</t>
+          <t>checkInstall</t>
         </is>
       </c>
     </row>
@@ -12092,70 +12093,71 @@
       </c>
       <c r="D295" s="3" t="inlineStr">
         <is>
+          <t>store/auth.js</t>
+        </is>
+      </c>
+      <c r="E295" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="F295" s="5" t="inlineStr">
+        <is>
+          <t>/auth/checkRemote/{user}</t>
+        </is>
+      </c>
+      <c r="G295" s="5" t="inlineStr">
+        <is>
+          <t>routes/auth.py</t>
+        </is>
+      </c>
+      <c r="H295" s="3" t="inlineStr">
+        <is>
+          <t>check_remoteUser</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="3" t="n">
+        <v>286</v>
+      </c>
+      <c r="B296" s="3" t="inlineStr">
+        <is>
+          <t>/settings/:mode/:channel</t>
+        </is>
+      </c>
+      <c r="C296" s="3" t="inlineStr">
+        <is>
+          <t>pages/main/SettingNew.vue</t>
+        </is>
+      </c>
+      <c r="D296" s="3" t="inlineStr">
+        <is>
           <t>store/setup.js</t>
         </is>
       </c>
-      <c r="E295" s="4" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="F295" s="5" t="inlineStr">
+      <c r="E296" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="F296" s="5" t="inlineStr">
         <is>
           <t>/setting/checkSettingFile</t>
         </is>
       </c>
-      <c r="G295" s="5" t="inlineStr">
+      <c r="G296" s="5" t="inlineStr">
         <is>
           <t>routes/setting.py</t>
         </is>
       </c>
-      <c r="H295" s="3" t="inlineStr">
+      <c r="H296" s="3" t="inlineStr">
         <is>
           <t>check_setupfile</t>
         </is>
       </c>
     </row>
-    <row r="297">
-      <c r="A297" s="3" t="n">
-        <v>286</v>
-      </c>
-      <c r="B297" s="3" t="inlineStr">
-        <is>
-          <t>/config/:channel</t>
-        </is>
-      </c>
-      <c r="C297" s="3" t="inlineStr">
-        <is>
-          <t>pages/main/Calibrate2.vue</t>
-        </is>
-      </c>
-      <c r="D297" s="3" t="inlineStr">
-        <is>
-          <t>pages/common/Header.vue</t>
-        </is>
-      </c>
-      <c r="E297" s="4" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="F297" s="5" t="inlineStr">
-        <is>
-          <t>/api/getSystemStatus</t>
-        </is>
-      </c>
-      <c r="G297" s="5" t="inlineStr">
-        <is>
-          <t>routes/api.py</t>
-        </is>
-      </c>
-      <c r="H297" s="3" t="inlineStr">
-        <is>
-          <t>get_service</t>
-        </is>
-      </c>
-    </row>
+    <row r="297"/>
     <row r="298">
       <c r="A298" s="3" t="n">
         <v>287</v>
@@ -12172,27 +12174,27 @@
       </c>
       <c r="D298" s="3" t="inlineStr">
         <is>
-          <t>pages/header/DropdownClock.vue</t>
+          <t>pages/common/Header.vue</t>
         </is>
       </c>
       <c r="E298" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="F298" s="5" t="inlineStr">
         <is>
-          <t>/config/checktime</t>
+          <t>/api/getSystemStatus</t>
         </is>
       </c>
       <c r="G298" s="5" t="inlineStr">
         <is>
-          <t>routes/config.py</t>
+          <t>routes/api.py</t>
         </is>
       </c>
       <c r="H298" s="3" t="inlineStr">
         <is>
-          <t>check_device_time</t>
+          <t>get_service</t>
         </is>
       </c>
     </row>
@@ -12222,17 +12224,17 @@
       </c>
       <c r="F299" s="5" t="inlineStr">
         <is>
-          <t>/setting/setSystemTime</t>
+          <t>/config/checktime</t>
         </is>
       </c>
       <c r="G299" s="5" t="inlineStr">
         <is>
-          <t>routes/setting.py</t>
+          <t>routes/config.py</t>
         </is>
       </c>
       <c r="H299" s="3" t="inlineStr">
         <is>
-          <t>setup_system_time</t>
+          <t>check_device_time</t>
         </is>
       </c>
     </row>
@@ -12252,27 +12254,27 @@
       </c>
       <c r="D300" s="3" t="inlineStr">
         <is>
-          <t>pages/header/DropdownHelp.vue</t>
+          <t>pages/header/DropdownClock.vue</t>
         </is>
       </c>
       <c r="E300" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="F300" s="5" t="inlineStr">
         <is>
-          <t>/api/download/{mode}/{lang}</t>
+          <t>/setting/setSystemTime</t>
         </is>
       </c>
       <c r="G300" s="5" t="inlineStr">
         <is>
-          <t>routes/api.py</t>
+          <t>routes/setting.py</t>
         </is>
       </c>
       <c r="H300" s="3" t="inlineStr">
         <is>
-          <t>get_deviceDoc</t>
+          <t>setup_system_time</t>
         </is>
       </c>
     </row>
@@ -12292,7 +12294,7 @@
       </c>
       <c r="D301" s="3" t="inlineStr">
         <is>
-          <t>pages/main/Calibrate2.vue</t>
+          <t>pages/header/DropdownHelp.vue</t>
         </is>
       </c>
       <c r="E301" s="4" t="inlineStr">
@@ -12302,17 +12304,17 @@
       </c>
       <c r="F301" s="5" t="inlineStr">
         <is>
-          <t>/config/calibrateNow</t>
+          <t>/api/download/{mode}/{lang}</t>
         </is>
       </c>
       <c r="G301" s="5" t="inlineStr">
         <is>
-          <t>routes/config.py</t>
+          <t>routes/api.py</t>
         </is>
       </c>
       <c r="H301" s="3" t="inlineStr">
         <is>
-          <t>cali_mount</t>
+          <t>get_deviceDoc</t>
         </is>
       </c>
     </row>
@@ -12332,7 +12334,7 @@
       </c>
       <c r="D302" s="3" t="inlineStr">
         <is>
-          <t>partials/inners/config/CaliPanel2.vue</t>
+          <t>pages/main/Calibrate2.vue</t>
         </is>
       </c>
       <c r="E302" s="4" t="inlineStr">
@@ -12372,17 +12374,17 @@
       </c>
       <c r="D303" s="3" t="inlineStr">
         <is>
-          <t>partials/inners/config/CaliSideBar2.vue</t>
+          <t>partials/inners/config/CaliPanel2.vue</t>
         </is>
       </c>
       <c r="E303" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="F303" s="5" t="inlineStr">
         <is>
-          <t>/config/calibrate/saveRef</t>
+          <t>/config/calibrateNow</t>
         </is>
       </c>
       <c r="G303" s="5" t="inlineStr">
@@ -12392,7 +12394,7 @@
       </c>
       <c r="H303" s="3" t="inlineStr">
         <is>
-          <t>set_saveref</t>
+          <t>cali_mount</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12419,12 @@
       </c>
       <c r="E304" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="F304" s="5" t="inlineStr">
         <is>
-          <t>/config/calibrate/start</t>
+          <t>/config/calibrate/saveRef</t>
         </is>
       </c>
       <c r="G304" s="5" t="inlineStr">
@@ -12432,7 +12434,7 @@
       </c>
       <c r="H304" s="3" t="inlineStr">
         <is>
-          <t>cali_start</t>
+          <t>set_saveref</t>
         </is>
       </c>
     </row>
@@ -12462,7 +12464,7 @@
       </c>
       <c r="F305" s="5" t="inlineStr">
         <is>
-          <t>/config/calibrate/end</t>
+          <t>/config/calibrate/start</t>
         </is>
       </c>
       <c r="G305" s="5" t="inlineStr">
@@ -12472,7 +12474,7 @@
       </c>
       <c r="H305" s="3" t="inlineStr">
         <is>
-          <t>cali_end</t>
+          <t>cali_start</t>
         </is>
       </c>
     </row>
@@ -12497,12 +12499,12 @@
       </c>
       <c r="E306" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="F306" s="5" t="inlineStr">
         <is>
-          <t>/config/calibrate/cmd</t>
+          <t>/config/calibrate/end</t>
         </is>
       </c>
       <c r="G306" s="5" t="inlineStr">
@@ -12512,7 +12514,7 @@
       </c>
       <c r="H306" s="3" t="inlineStr">
         <is>
-          <t>set_cmd</t>
+          <t>cali_end</t>
         </is>
       </c>
     </row>
@@ -12542,7 +12544,7 @@
       </c>
       <c r="F307" s="5" t="inlineStr">
         <is>
-          <t>/config/calibrate/setSystemTime</t>
+          <t>/config/calibrate/cmd</t>
         </is>
       </c>
       <c r="G307" s="5" t="inlineStr">
@@ -12552,7 +12554,7 @@
       </c>
       <c r="H307" s="3" t="inlineStr">
         <is>
-          <t>set_system_time</t>
+          <t>set_cmd</t>
         </is>
       </c>
     </row>
@@ -12582,7 +12584,7 @@
       </c>
       <c r="F308" s="5" t="inlineStr">
         <is>
-          <t>/config/upload</t>
+          <t>/config/calibrate/setSystemTime</t>
         </is>
       </c>
       <c r="G308" s="5" t="inlineStr">
@@ -12592,7 +12594,7 @@
       </c>
       <c r="H308" s="3" t="inlineStr">
         <is>
-          <t>upload_file</t>
+          <t>set_system_time</t>
         </is>
       </c>
     </row>
@@ -12617,12 +12619,12 @@
       </c>
       <c r="E309" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="F309" s="5" t="inlineStr">
         <is>
-          <t>/config/calibrate/applySetup</t>
+          <t>/config/upload</t>
         </is>
       </c>
       <c r="G309" s="5" t="inlineStr">
@@ -12632,7 +12634,7 @@
       </c>
       <c r="H309" s="3" t="inlineStr">
         <is>
-          <t>cali_setup</t>
+          <t>upload_file</t>
         </is>
       </c>
     </row>
@@ -12662,7 +12664,7 @@
       </c>
       <c r="F310" s="5" t="inlineStr">
         <is>
-          <t>/config/checkSetup</t>
+          <t>/config/calibrate/applySetup</t>
         </is>
       </c>
       <c r="G310" s="5" t="inlineStr">
@@ -12672,7 +12674,7 @@
       </c>
       <c r="H310" s="3" t="inlineStr">
         <is>
-          <t>check_setup</t>
+          <t>cali_setup</t>
         </is>
       </c>
     </row>
@@ -12702,7 +12704,7 @@
       </c>
       <c r="F311" s="5" t="inlineStr">
         <is>
-          <t>/config/calibrate/gettime</t>
+          <t>/config/checkSetup</t>
         </is>
       </c>
       <c r="G311" s="5" t="inlineStr">
@@ -12712,7 +12714,7 @@
       </c>
       <c r="H311" s="3" t="inlineStr">
         <is>
-          <t>get_device_time</t>
+          <t>check_setup</t>
         </is>
       </c>
     </row>
@@ -12732,7 +12734,7 @@
       </c>
       <c r="D312" s="3" t="inlineStr">
         <is>
-          <t>partials/inners/config/CommandPanel.vue</t>
+          <t>partials/inners/config/CaliSideBar2.vue</t>
         </is>
       </c>
       <c r="E312" s="4" t="inlineStr">
@@ -12742,17 +12744,17 @@
       </c>
       <c r="F312" s="5" t="inlineStr">
         <is>
-          <t>/setting/updateSmartSystem/{mode}</t>
+          <t>/config/calibrate/gettime</t>
         </is>
       </c>
       <c r="G312" s="5" t="inlineStr">
         <is>
-          <t>routes/setting.py</t>
+          <t>routes/config.py</t>
         </is>
       </c>
       <c r="H312" s="3" t="inlineStr">
         <is>
-          <t>update_smartsystem</t>
+          <t>get_device_time</t>
         </is>
       </c>
     </row>
@@ -12777,12 +12779,12 @@
       </c>
       <c r="E313" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="F313" s="5" t="inlineStr">
         <is>
-          <t>/setting/backup/start</t>
+          <t>/setting/updateSmartSystem/{mode}</t>
         </is>
       </c>
       <c r="G313" s="5" t="inlineStr">
@@ -12792,7 +12794,7 @@
       </c>
       <c r="H313" s="3" t="inlineStr">
         <is>
-          <t>start_backup</t>
+          <t>update_smartsystem</t>
         </is>
       </c>
     </row>
@@ -12817,12 +12819,12 @@
       </c>
       <c r="E314" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="F314" s="5" t="inlineStr">
         <is>
-          <t>/setting/backup/status/{task_id}</t>
+          <t>/setting/backup/start</t>
         </is>
       </c>
       <c r="G314" s="5" t="inlineStr">
@@ -12832,7 +12834,7 @@
       </c>
       <c r="H314" s="3" t="inlineStr">
         <is>
-          <t>get_backup_status</t>
+          <t>start_backup</t>
         </is>
       </c>
     </row>
@@ -12862,7 +12864,7 @@
       </c>
       <c r="F315" s="5" t="inlineStr">
         <is>
-          <t>/setting/SysCheck</t>
+          <t>/setting/backup/status/{task_id}</t>
         </is>
       </c>
       <c r="G315" s="5" t="inlineStr">
@@ -12872,7 +12874,7 @@
       </c>
       <c r="H315" s="3" t="inlineStr">
         <is>
-          <t>check_sysStatus</t>
+          <t>get_backup_status</t>
         </is>
       </c>
     </row>
@@ -12892,7 +12894,7 @@
       </c>
       <c r="D316" s="3" t="inlineStr">
         <is>
-          <t>partials/inners/config/LogPanel.vue</t>
+          <t>partials/inners/config/CommandPanel.vue</t>
         </is>
       </c>
       <c r="E316" s="4" t="inlineStr">
@@ -12902,17 +12904,17 @@
       </c>
       <c r="F316" s="5" t="inlineStr">
         <is>
-          <t>/config/getLog</t>
+          <t>/setting/SysCheck</t>
         </is>
       </c>
       <c r="G316" s="5" t="inlineStr">
         <is>
-          <t>routes/config.py</t>
+          <t>routes/setting.py</t>
         </is>
       </c>
       <c r="H316" s="3" t="inlineStr">
         <is>
-          <t>get_log</t>
+          <t>check_sysStatus</t>
         </is>
       </c>
     </row>
@@ -12937,12 +12939,12 @@
       </c>
       <c r="E317" s="4" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="F317" s="5" t="inlineStr">
         <is>
-          <t>/config/deleteLog</t>
+          <t>/config/getLog</t>
         </is>
       </c>
       <c r="G317" s="5" t="inlineStr">
@@ -12952,7 +12954,7 @@
       </c>
       <c r="H317" s="3" t="inlineStr">
         <is>
-          <t>delete_all_logs</t>
+          <t>get_log</t>
         </is>
       </c>
     </row>
@@ -12972,17 +12974,17 @@
       </c>
       <c r="D318" s="3" t="inlineStr">
         <is>
-          <t>partials/inners/config/MaintenancePanel.vue</t>
+          <t>partials/inners/config/LogPanel.vue</t>
         </is>
       </c>
       <c r="E318" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="F318" s="5" t="inlineStr">
         <is>
-          <t>/config/getReleaseNotes</t>
+          <t>/config/deleteLog</t>
         </is>
       </c>
       <c r="G318" s="5" t="inlineStr">
@@ -12992,7 +12994,7 @@
       </c>
       <c r="H318" s="3" t="inlineStr">
         <is>
-          <t>get_release_notes</t>
+          <t>delete_all_logs</t>
         </is>
       </c>
     </row>
@@ -13022,7 +13024,7 @@
       </c>
       <c r="F319" s="5" t="inlineStr">
         <is>
-          <t>/config/getReleaseNote/{lang}/{version}</t>
+          <t>/config/getReleaseNotes</t>
         </is>
       </c>
       <c r="G319" s="5" t="inlineStr">
@@ -13032,7 +13034,7 @@
       </c>
       <c r="H319" s="3" t="inlineStr">
         <is>
-          <t>get_release_note</t>
+          <t>get_release_notes</t>
         </is>
       </c>
     </row>
@@ -13057,12 +13059,12 @@
       </c>
       <c r="E320" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="F320" s="5" t="inlineStr">
         <is>
-          <t>/config/savePost/{mode}/{idx}</t>
+          <t>/config/getReleaseNote/{lang}/{version}</t>
         </is>
       </c>
       <c r="G320" s="5" t="inlineStr">
@@ -13072,7 +13074,7 @@
       </c>
       <c r="H320" s="3" t="inlineStr">
         <is>
-          <t>save_maintanence</t>
+          <t>get_release_note</t>
         </is>
       </c>
     </row>
@@ -13097,12 +13099,12 @@
       </c>
       <c r="E321" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="F321" s="5" t="inlineStr">
         <is>
-          <t>/config/getPost</t>
+          <t>/config/savePost/{mode}/{idx}</t>
         </is>
       </c>
       <c r="G321" s="5" t="inlineStr">
@@ -13112,7 +13114,7 @@
       </c>
       <c r="H321" s="3" t="inlineStr">
         <is>
-          <t>get_post</t>
+          <t>save_maintanence</t>
         </is>
       </c>
     </row>
@@ -13142,7 +13144,7 @@
       </c>
       <c r="F322" s="5" t="inlineStr">
         <is>
-          <t>/config/getLastPost</t>
+          <t>/config/getPost</t>
         </is>
       </c>
       <c r="G322" s="5" t="inlineStr">
@@ -13152,7 +13154,7 @@
       </c>
       <c r="H322" s="3" t="inlineStr">
         <is>
-          <t>get_last</t>
+          <t>get_post</t>
         </is>
       </c>
     </row>
@@ -13182,7 +13184,7 @@
       </c>
       <c r="F323" s="5" t="inlineStr">
         <is>
-          <t>/config/deletePost/{idx}</t>
+          <t>/config/getLastPost</t>
         </is>
       </c>
       <c r="G323" s="5" t="inlineStr">
@@ -13192,7 +13194,7 @@
       </c>
       <c r="H323" s="3" t="inlineStr">
         <is>
-          <t>delete_post</t>
+          <t>get_last</t>
         </is>
       </c>
     </row>
@@ -13212,7 +13214,7 @@
       </c>
       <c r="D324" s="3" t="inlineStr">
         <is>
-          <t>partials/inners/config/ServiceCard_New.vue</t>
+          <t>partials/inners/config/MaintenancePanel.vue</t>
         </is>
       </c>
       <c r="E324" s="4" t="inlineStr">
@@ -13222,17 +13224,17 @@
       </c>
       <c r="F324" s="5" t="inlineStr">
         <is>
-          <t>/setting/SysService/{cmd}/{item}</t>
+          <t>/config/deletePost/{idx}</t>
         </is>
       </c>
       <c r="G324" s="5" t="inlineStr">
         <is>
-          <t>routes/setting.py</t>
+          <t>routes/config.py</t>
         </is>
       </c>
       <c r="H324" s="3" t="inlineStr">
         <is>
-          <t>control_service</t>
+          <t>delete_post</t>
         </is>
       </c>
     </row>
@@ -13252,7 +13254,7 @@
       </c>
       <c r="D325" s="3" t="inlineStr">
         <is>
-          <t>partials/inners/config/ServicePanel_New.vue</t>
+          <t>partials/inners/config/ServiceCard_New.vue</t>
         </is>
       </c>
       <c r="E325" s="4" t="inlineStr">
@@ -13262,7 +13264,7 @@
       </c>
       <c r="F325" s="5" t="inlineStr">
         <is>
-          <t>/setting/SysCheck</t>
+          <t>/setting/SysService/{cmd}/{item}</t>
         </is>
       </c>
       <c r="G325" s="5" t="inlineStr">
@@ -13272,7 +13274,7 @@
       </c>
       <c r="H325" s="3" t="inlineStr">
         <is>
-          <t>check_sysStatus</t>
+          <t>control_service</t>
         </is>
       </c>
     </row>
@@ -13302,7 +13304,7 @@
       </c>
       <c r="F326" s="5" t="inlineStr">
         <is>
-          <t>/setting/checkSmartStatus</t>
+          <t>/setting/SysCheck</t>
         </is>
       </c>
       <c r="G326" s="5" t="inlineStr">
@@ -13312,7 +13314,7 @@
       </c>
       <c r="H326" s="3" t="inlineStr">
         <is>
-          <t>check_SmartStatus</t>
+          <t>check_sysStatus</t>
         </is>
       </c>
     </row>
@@ -13342,7 +13344,7 @@
       </c>
       <c r="F327" s="5" t="inlineStr">
         <is>
-          <t>/setting/initDB/status</t>
+          <t>/setting/checkSmartStatus</t>
         </is>
       </c>
       <c r="G327" s="5" t="inlineStr">
@@ -13352,7 +13354,7 @@
       </c>
       <c r="H327" s="3" t="inlineStr">
         <is>
-          <t>get_init_status</t>
+          <t>check_SmartStatus</t>
         </is>
       </c>
     </row>
@@ -13382,7 +13384,7 @@
       </c>
       <c r="F328" s="5" t="inlineStr">
         <is>
-          <t>/setting/checkInfluxStatus</t>
+          <t>/setting/initDB/status</t>
         </is>
       </c>
       <c r="G328" s="5" t="inlineStr">
@@ -13392,7 +13394,7 @@
       </c>
       <c r="H328" s="3" t="inlineStr">
         <is>
-          <t>check_influxStatus</t>
+          <t>get_init_status</t>
         </is>
       </c>
     </row>
@@ -13422,7 +13424,7 @@
       </c>
       <c r="F329" s="5" t="inlineStr">
         <is>
-          <t>/setting/checkFrp</t>
+          <t>/setting/checkInfluxStatus</t>
         </is>
       </c>
       <c r="G329" s="5" t="inlineStr">
@@ -13432,7 +13434,7 @@
       </c>
       <c r="H329" s="3" t="inlineStr">
         <is>
-          <t>check_frp</t>
+          <t>check_influxStatus</t>
         </is>
       </c>
     </row>
@@ -13462,7 +13464,7 @@
       </c>
       <c r="F330" s="5" t="inlineStr">
         <is>
-          <t>/setting/initDB</t>
+          <t>/setting/checkFrp</t>
         </is>
       </c>
       <c r="G330" s="5" t="inlineStr">
@@ -13472,7 +13474,7 @@
       </c>
       <c r="H330" s="3" t="inlineStr">
         <is>
-          <t>initInflux</t>
+          <t>check_frp</t>
         </is>
       </c>
     </row>
@@ -13502,7 +13504,7 @@
       </c>
       <c r="F331" s="5" t="inlineStr">
         <is>
-          <t>/setting/setup-downsampling</t>
+          <t>/setting/initDB</t>
         </is>
       </c>
       <c r="G331" s="5" t="inlineStr">
@@ -13512,7 +13514,7 @@
       </c>
       <c r="H331" s="3" t="inlineStr">
         <is>
-          <t>setup_downsampling_endpoint</t>
+          <t>initInflux</t>
         </is>
       </c>
     </row>
@@ -13542,7 +13544,7 @@
       </c>
       <c r="F332" s="5" t="inlineStr">
         <is>
-          <t>/setting/ResetAll</t>
+          <t>/setting/setup-downsampling</t>
         </is>
       </c>
       <c r="G332" s="5" t="inlineStr">
@@ -13552,7 +13554,7 @@
       </c>
       <c r="H332" s="3" t="inlineStr">
         <is>
-          <t>resetAll</t>
+          <t>setup_downsampling_endpoint</t>
         </is>
       </c>
     </row>
@@ -13582,7 +13584,7 @@
       </c>
       <c r="F333" s="5" t="inlineStr">
         <is>
-          <t>/setting/backup/parquet/report/list</t>
+          <t>/setting/ResetAll</t>
         </is>
       </c>
       <c r="G333" s="5" t="inlineStr">
@@ -13592,7 +13594,7 @@
       </c>
       <c r="H333" s="3" t="inlineStr">
         <is>
-          <t>list_report_files</t>
+          <t>resetAll</t>
         </is>
       </c>
     </row>
@@ -13622,17 +13624,17 @@
       </c>
       <c r="F334" s="5" t="inlineStr">
         <is>
-          <t>/config/getTrain/status/{task_id}</t>
+          <t>/setting/backup/parquet/report/list</t>
         </is>
       </c>
       <c r="G334" s="5" t="inlineStr">
         <is>
-          <t>routes/config.py</t>
+          <t>routes/setting.py</t>
         </is>
       </c>
       <c r="H334" s="3" t="inlineStr">
         <is>
-          <t>get_train_status</t>
+          <t>list_report_files</t>
         </is>
       </c>
     </row>
@@ -13662,7 +13664,7 @@
       </c>
       <c r="F335" s="5" t="inlineStr">
         <is>
-          <t>/config/getTrain/range/{channel}</t>
+          <t>/config/getTrain/status/{task_id}</t>
         </is>
       </c>
       <c r="G335" s="5" t="inlineStr">
@@ -13672,7 +13674,7 @@
       </c>
       <c r="H335" s="3" t="inlineStr">
         <is>
-          <t>get_train_range</t>
+          <t>get_train_status</t>
         </is>
       </c>
     </row>
@@ -13697,12 +13699,12 @@
       </c>
       <c r="E336" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="F336" s="5" t="inlineStr">
         <is>
-          <t>/config/getTrain/start/{channel}/{start}</t>
+          <t>/config/getTrain/range/{channel}</t>
         </is>
       </c>
       <c r="G336" s="5" t="inlineStr">
@@ -13712,7 +13714,7 @@
       </c>
       <c r="H336" s="3" t="inlineStr">
         <is>
-          <t>start_train_collect</t>
+          <t>get_train_range</t>
         </is>
       </c>
     </row>
@@ -13737,12 +13739,12 @@
       </c>
       <c r="E337" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="F337" s="5" t="inlineStr">
         <is>
-          <t>/config/getTrain/download/{channel}/{start}</t>
+          <t>/config/getTrain/start/{channel}/{start}</t>
         </is>
       </c>
       <c r="G337" s="5" t="inlineStr">
@@ -13752,7 +13754,7 @@
       </c>
       <c r="H337" s="3" t="inlineStr">
         <is>
-          <t>download_train</t>
+          <t>start_train_collect</t>
         </is>
       </c>
     </row>
@@ -13782,17 +13784,17 @@
       </c>
       <c r="F338" s="5" t="inlineStr">
         <is>
-          <t>/setting/backup/parquet/report/download</t>
+          <t>/config/getTrain/download/{channel}/{start}</t>
         </is>
       </c>
       <c r="G338" s="5" t="inlineStr">
         <is>
-          <t>routes/setting.py</t>
+          <t>routes/config.py</t>
         </is>
       </c>
       <c r="H338" s="3" t="inlineStr">
         <is>
-          <t>download_report_parquet</t>
+          <t>download_train</t>
         </is>
       </c>
     </row>
@@ -13822,7 +13824,7 @@
       </c>
       <c r="F339" s="5" t="inlineStr">
         <is>
-          <t>/setting/backup/parquet/report/download-all</t>
+          <t>/setting/backup/parquet/report/download</t>
         </is>
       </c>
       <c r="G339" s="5" t="inlineStr">
@@ -13832,7 +13834,7 @@
       </c>
       <c r="H339" s="3" t="inlineStr">
         <is>
-          <t>download_all_reports</t>
+          <t>download_report_parquet</t>
         </is>
       </c>
     </row>
@@ -13857,22 +13859,22 @@
       </c>
       <c r="E340" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="F340" s="5" t="inlineStr">
         <is>
-          <t>/api/downloadTrendCsv/{channel}</t>
+          <t>/setting/backup/parquet/report/download-all</t>
         </is>
       </c>
       <c r="G340" s="5" t="inlineStr">
         <is>
-          <t>routes/api.py</t>
+          <t>routes/setting.py</t>
         </is>
       </c>
       <c r="H340" s="3" t="inlineStr">
         <is>
-          <t>downloadTrendCsv</t>
+          <t>download_all_reports</t>
         </is>
       </c>
     </row>
@@ -13902,17 +13904,17 @@
       </c>
       <c r="F341" s="5" t="inlineStr">
         <is>
-          <t>/setting/setDefaultIP</t>
+          <t>/api/downloadTrendCsv/{channel}</t>
         </is>
       </c>
       <c r="G341" s="5" t="inlineStr">
         <is>
-          <t>routes/setting.py</t>
+          <t>routes/api.py</t>
         </is>
       </c>
       <c r="H341" s="3" t="inlineStr">
         <is>
-          <t>set_defaultIP</t>
+          <t>downloadTrendCsv</t>
         </is>
       </c>
     </row>
@@ -13932,17 +13934,17 @@
       </c>
       <c r="D342" s="3" t="inlineStr">
         <is>
-          <t>partials/inners/setting/CommandItem.vue</t>
+          <t>partials/inners/config/ServicePanel_New.vue</t>
         </is>
       </c>
       <c r="E342" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="F342" s="5" t="inlineStr">
         <is>
-          <t>/setting/SysService/{cmd}/{item}</t>
+          <t>/setting/setDefaultIP</t>
         </is>
       </c>
       <c r="G342" s="5" t="inlineStr">
@@ -13952,7 +13954,7 @@
       </c>
       <c r="H342" s="3" t="inlineStr">
         <is>
-          <t>control_service</t>
+          <t>set_defaultIP</t>
         </is>
       </c>
     </row>
@@ -13977,12 +13979,12 @@
       </c>
       <c r="E343" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="F343" s="5" t="inlineStr">
         <is>
-          <t>/setting/command</t>
+          <t>/setting/SysService/{cmd}/{item}</t>
         </is>
       </c>
       <c r="G343" s="5" t="inlineStr">
@@ -13992,7 +13994,7 @@
       </c>
       <c r="H343" s="3" t="inlineStr">
         <is>
-          <t>push_command_left</t>
+          <t>control_service</t>
         </is>
       </c>
     </row>
@@ -14017,22 +14019,22 @@
       </c>
       <c r="E344" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="F344" s="5" t="inlineStr">
         <is>
-          <t>/auth/checkDBMS</t>
+          <t>/setting/command</t>
         </is>
       </c>
       <c r="G344" s="5" t="inlineStr">
         <is>
-          <t>routes/auth.py</t>
+          <t>routes/setting.py</t>
         </is>
       </c>
       <c r="H344" s="3" t="inlineStr">
         <is>
-          <t>check_Db</t>
+          <t>push_command_left</t>
         </is>
       </c>
     </row>
@@ -14062,17 +14064,17 @@
       </c>
       <c r="F345" s="5" t="inlineStr">
         <is>
-          <t>/setting/initDB</t>
+          <t>/auth/checkDBMS</t>
         </is>
       </c>
       <c r="G345" s="5" t="inlineStr">
         <is>
-          <t>routes/setting.py</t>
+          <t>routes/auth.py</t>
         </is>
       </c>
       <c r="H345" s="3" t="inlineStr">
         <is>
-          <t>initInflux</t>
+          <t>check_Db</t>
         </is>
       </c>
     </row>
@@ -14102,7 +14104,7 @@
       </c>
       <c r="F346" s="5" t="inlineStr">
         <is>
-          <t>/setting/ResetAll</t>
+          <t>/setting/initDB</t>
         </is>
       </c>
       <c r="G346" s="5" t="inlineStr">
@@ -14112,7 +14114,7 @@
       </c>
       <c r="H346" s="3" t="inlineStr">
         <is>
-          <t>resetAll</t>
+          <t>initInflux</t>
         </is>
       </c>
     </row>
@@ -14142,7 +14144,7 @@
       </c>
       <c r="F347" s="5" t="inlineStr">
         <is>
-          <t>/setting/Reset</t>
+          <t>/setting/ResetAll</t>
         </is>
       </c>
       <c r="G347" s="5" t="inlineStr">
@@ -14152,7 +14154,7 @@
       </c>
       <c r="H347" s="3" t="inlineStr">
         <is>
-          <t>reset</t>
+          <t>resetAll</t>
         </is>
       </c>
     </row>
@@ -14177,12 +14179,12 @@
       </c>
       <c r="E348" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="F348" s="5" t="inlineStr">
         <is>
-          <t>/setting/upload</t>
+          <t>/setting/Reset</t>
         </is>
       </c>
       <c r="G348" s="5" t="inlineStr">
@@ -14192,7 +14194,7 @@
       </c>
       <c r="H348" s="3" t="inlineStr">
         <is>
-          <t>upload_file</t>
+          <t>reset</t>
         </is>
       </c>
     </row>
@@ -14217,12 +14219,12 @@
       </c>
       <c r="E349" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="F349" s="5" t="inlineStr">
         <is>
-          <t>/setting/download</t>
+          <t>/setting/upload</t>
         </is>
       </c>
       <c r="G349" s="5" t="inlineStr">
@@ -14232,7 +14234,7 @@
       </c>
       <c r="H349" s="3" t="inlineStr">
         <is>
-          <t>download_setting</t>
+          <t>upload_file</t>
         </is>
       </c>
     </row>
@@ -14257,12 +14259,12 @@
       </c>
       <c r="E350" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="F350" s="5" t="inlineStr">
         <is>
-          <t>/setting/restoreSetting</t>
+          <t>/setting/download</t>
         </is>
       </c>
       <c r="G350" s="5" t="inlineStr">
@@ -14272,7 +14274,7 @@
       </c>
       <c r="H350" s="3" t="inlineStr">
         <is>
-          <t>restore_setting</t>
+          <t>download_setting</t>
         </is>
       </c>
     </row>
@@ -14292,7 +14294,7 @@
       </c>
       <c r="D351" s="3" t="inlineStr">
         <is>
-          <t>store/auth.js</t>
+          <t>partials/inners/setting/CommandItem.vue</t>
         </is>
       </c>
       <c r="E351" s="4" t="inlineStr">
@@ -14302,17 +14304,17 @@
       </c>
       <c r="F351" s="5" t="inlineStr">
         <is>
-          <t>/auth/checkLogins</t>
+          <t>/setting/restoreSetting</t>
         </is>
       </c>
       <c r="G351" s="5" t="inlineStr">
         <is>
-          <t>routes/auth.py</t>
+          <t>routes/setting.py</t>
         </is>
       </c>
       <c r="H351" s="3" t="inlineStr">
         <is>
-          <t>checkLogins</t>
+          <t>restore_setting</t>
         </is>
       </c>
     </row>
@@ -14337,12 +14339,12 @@
       </c>
       <c r="E352" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="F352" s="5" t="inlineStr">
         <is>
-          <t>/auth/logout</t>
+          <t>/auth/checkLogins</t>
         </is>
       </c>
       <c r="G352" s="5" t="inlineStr">
@@ -14352,7 +14354,7 @@
       </c>
       <c r="H352" s="3" t="inlineStr">
         <is>
-          <t>logout</t>
+          <t>checkLogins</t>
         </is>
       </c>
     </row>
@@ -14382,7 +14384,7 @@
       </c>
       <c r="F353" s="5" t="inlineStr">
         <is>
-          <t>/auth/checkSession</t>
+          <t>/auth/logout</t>
         </is>
       </c>
       <c r="G353" s="5" t="inlineStr">
@@ -14392,7 +14394,7 @@
       </c>
       <c r="H353" s="3" t="inlineStr">
         <is>
-          <t>check_session</t>
+          <t>logout</t>
         </is>
       </c>
     </row>
@@ -14422,7 +14424,7 @@
       </c>
       <c r="F354" s="5" t="inlineStr">
         <is>
-          <t>/auth/checkInstall</t>
+          <t>/auth/checkSession</t>
         </is>
       </c>
       <c r="G354" s="5" t="inlineStr">
@@ -14432,7 +14434,7 @@
       </c>
       <c r="H354" s="3" t="inlineStr">
         <is>
-          <t>checkInstall</t>
+          <t>check_session</t>
         </is>
       </c>
     </row>
@@ -14462,7 +14464,7 @@
       </c>
       <c r="F355" s="5" t="inlineStr">
         <is>
-          <t>/auth/checkRemote/{user}</t>
+          <t>/auth/checkInstall</t>
         </is>
       </c>
       <c r="G355" s="5" t="inlineStr">
@@ -14472,7 +14474,7 @@
       </c>
       <c r="H355" s="3" t="inlineStr">
         <is>
-          <t>check_remoteUser</t>
+          <t>checkInstall</t>
         </is>
       </c>
     </row>
@@ -14492,70 +14494,71 @@
       </c>
       <c r="D356" s="3" t="inlineStr">
         <is>
+          <t>store/auth.js</t>
+        </is>
+      </c>
+      <c r="E356" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="F356" s="5" t="inlineStr">
+        <is>
+          <t>/auth/checkRemote/{user}</t>
+        </is>
+      </c>
+      <c r="G356" s="5" t="inlineStr">
+        <is>
+          <t>routes/auth.py</t>
+        </is>
+      </c>
+      <c r="H356" s="3" t="inlineStr">
+        <is>
+          <t>check_remoteUser</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="3" t="n">
+        <v>346</v>
+      </c>
+      <c r="B357" s="3" t="inlineStr">
+        <is>
+          <t>/config/:channel</t>
+        </is>
+      </c>
+      <c r="C357" s="3" t="inlineStr">
+        <is>
+          <t>pages/main/Calibrate2.vue</t>
+        </is>
+      </c>
+      <c r="D357" s="3" t="inlineStr">
+        <is>
           <t>store/setup.js</t>
         </is>
       </c>
-      <c r="E356" s="4" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="F356" s="5" t="inlineStr">
+      <c r="E357" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="F357" s="5" t="inlineStr">
         <is>
           <t>/setting/checkSettingFile</t>
         </is>
       </c>
-      <c r="G356" s="5" t="inlineStr">
+      <c r="G357" s="5" t="inlineStr">
         <is>
           <t>routes/setting.py</t>
         </is>
       </c>
-      <c r="H356" s="3" t="inlineStr">
+      <c r="H357" s="3" t="inlineStr">
         <is>
           <t>check_setupfile</t>
         </is>
       </c>
     </row>
-    <row r="358">
-      <c r="A358" s="3" t="n">
-        <v>346</v>
-      </c>
-      <c r="B358" s="3" t="inlineStr">
-        <is>
-          <t>/signin</t>
-        </is>
-      </c>
-      <c r="C358" s="3" t="inlineStr">
-        <is>
-          <t>pages/main/Signin.vue</t>
-        </is>
-      </c>
-      <c r="D358" s="3" t="inlineStr">
-        <is>
-          <t>pages/main/Signin.vue</t>
-        </is>
-      </c>
-      <c r="E358" s="4" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="F358" s="5" t="inlineStr">
-        <is>
-          <t>/auth/resetPassword</t>
-        </is>
-      </c>
-      <c r="G358" s="5" t="inlineStr">
-        <is>
-          <t>routes/auth.py</t>
-        </is>
-      </c>
-      <c r="H358" s="3" t="inlineStr">
-        <is>
-          <t>resetPassword</t>
-        </is>
-      </c>
-    </row>
+    <row r="358"/>
     <row r="359">
       <c r="A359" s="3" t="n">
         <v>347</v>
@@ -14572,7 +14575,7 @@
       </c>
       <c r="D359" s="3" t="inlineStr">
         <is>
-          <t>store/auth.js</t>
+          <t>pages/main/Signin.vue</t>
         </is>
       </c>
       <c r="E359" s="4" t="inlineStr">
@@ -14582,7 +14585,7 @@
       </c>
       <c r="F359" s="5" t="inlineStr">
         <is>
-          <t>/auth/checkLogins</t>
+          <t>/auth/resetPassword</t>
         </is>
       </c>
       <c r="G359" s="5" t="inlineStr">
@@ -14592,7 +14595,7 @@
       </c>
       <c r="H359" s="3" t="inlineStr">
         <is>
-          <t>checkLogins</t>
+          <t>resetPassword</t>
         </is>
       </c>
     </row>
@@ -14617,12 +14620,12 @@
       </c>
       <c r="E360" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="F360" s="5" t="inlineStr">
         <is>
-          <t>/auth/logout</t>
+          <t>/auth/checkLogins</t>
         </is>
       </c>
       <c r="G360" s="5" t="inlineStr">
@@ -14632,7 +14635,7 @@
       </c>
       <c r="H360" s="3" t="inlineStr">
         <is>
-          <t>logout</t>
+          <t>checkLogins</t>
         </is>
       </c>
     </row>
@@ -14662,7 +14665,7 @@
       </c>
       <c r="F361" s="5" t="inlineStr">
         <is>
-          <t>/auth/checkSession</t>
+          <t>/auth/logout</t>
         </is>
       </c>
       <c r="G361" s="5" t="inlineStr">
@@ -14672,7 +14675,7 @@
       </c>
       <c r="H361" s="3" t="inlineStr">
         <is>
-          <t>check_session</t>
+          <t>logout</t>
         </is>
       </c>
     </row>
@@ -14702,7 +14705,7 @@
       </c>
       <c r="F362" s="5" t="inlineStr">
         <is>
-          <t>/auth/checkInstall</t>
+          <t>/auth/checkSession</t>
         </is>
       </c>
       <c r="G362" s="5" t="inlineStr">
@@ -14712,7 +14715,7 @@
       </c>
       <c r="H362" s="3" t="inlineStr">
         <is>
-          <t>checkInstall</t>
+          <t>check_session</t>
         </is>
       </c>
     </row>
@@ -14742,7 +14745,7 @@
       </c>
       <c r="F363" s="5" t="inlineStr">
         <is>
-          <t>/auth/checkRemote/{user}</t>
+          <t>/auth/checkInstall</t>
         </is>
       </c>
       <c r="G363" s="5" t="inlineStr">
@@ -14752,7 +14755,7 @@
       </c>
       <c r="H363" s="3" t="inlineStr">
         <is>
-          <t>check_remoteUser</t>
+          <t>checkInstall</t>
         </is>
       </c>
     </row>
@@ -14772,70 +14775,71 @@
       </c>
       <c r="D364" s="3" t="inlineStr">
         <is>
+          <t>store/auth.js</t>
+        </is>
+      </c>
+      <c r="E364" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="F364" s="5" t="inlineStr">
+        <is>
+          <t>/auth/checkRemote/{user}</t>
+        </is>
+      </c>
+      <c r="G364" s="5" t="inlineStr">
+        <is>
+          <t>routes/auth.py</t>
+        </is>
+      </c>
+      <c r="H364" s="3" t="inlineStr">
+        <is>
+          <t>check_remoteUser</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="3" t="n">
+        <v>353</v>
+      </c>
+      <c r="B365" s="3" t="inlineStr">
+        <is>
+          <t>/signin</t>
+        </is>
+      </c>
+      <c r="C365" s="3" t="inlineStr">
+        <is>
+          <t>pages/main/Signin.vue</t>
+        </is>
+      </c>
+      <c r="D365" s="3" t="inlineStr">
+        <is>
           <t>store/setup.js</t>
         </is>
       </c>
-      <c r="E364" s="4" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="F364" s="5" t="inlineStr">
+      <c r="E365" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="F365" s="5" t="inlineStr">
         <is>
           <t>/setting/checkSettingFile</t>
         </is>
       </c>
-      <c r="G364" s="5" t="inlineStr">
+      <c r="G365" s="5" t="inlineStr">
         <is>
           <t>routes/setting.py</t>
         </is>
       </c>
-      <c r="H364" s="3" t="inlineStr">
+      <c r="H365" s="3" t="inlineStr">
         <is>
           <t>check_setupfile</t>
         </is>
       </c>
     </row>
-    <row r="366">
-      <c r="A366" s="3" t="n">
-        <v>353</v>
-      </c>
-      <c r="B366" s="3" t="inlineStr">
-        <is>
-          <t>/signup</t>
-        </is>
-      </c>
-      <c r="C366" s="3" t="inlineStr">
-        <is>
-          <t>pages/main/Signup.vue</t>
-        </is>
-      </c>
-      <c r="D366" s="3" t="inlineStr">
-        <is>
-          <t>pages/main/Signup.vue</t>
-        </is>
-      </c>
-      <c r="E366" s="4" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="F366" s="5" t="inlineStr">
-        <is>
-          <t>/auth/joinAdmin</t>
-        </is>
-      </c>
-      <c r="G366" s="5" t="inlineStr">
-        <is>
-          <t>routes/auth.py</t>
-        </is>
-      </c>
-      <c r="H366" s="3" t="inlineStr">
-        <is>
-          <t>join_admin</t>
-        </is>
-      </c>
-    </row>
+    <row r="366"/>
     <row r="367">
       <c r="A367" s="3" t="n">
         <v>354</v>
@@ -14852,7 +14856,7 @@
       </c>
       <c r="D367" s="3" t="inlineStr">
         <is>
-          <t>store/auth.js</t>
+          <t>pages/main/Signup.vue</t>
         </is>
       </c>
       <c r="E367" s="4" t="inlineStr">
@@ -14862,7 +14866,7 @@
       </c>
       <c r="F367" s="5" t="inlineStr">
         <is>
-          <t>/auth/checkLogins</t>
+          <t>/auth/joinAdmin</t>
         </is>
       </c>
       <c r="G367" s="5" t="inlineStr">
@@ -14872,7 +14876,7 @@
       </c>
       <c r="H367" s="3" t="inlineStr">
         <is>
-          <t>checkLogins</t>
+          <t>join_admin</t>
         </is>
       </c>
     </row>
@@ -14897,12 +14901,12 @@
       </c>
       <c r="E368" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="F368" s="5" t="inlineStr">
         <is>
-          <t>/auth/logout</t>
+          <t>/auth/checkLogins</t>
         </is>
       </c>
       <c r="G368" s="5" t="inlineStr">
@@ -14912,7 +14916,7 @@
       </c>
       <c r="H368" s="3" t="inlineStr">
         <is>
-          <t>logout</t>
+          <t>checkLogins</t>
         </is>
       </c>
     </row>
@@ -14942,7 +14946,7 @@
       </c>
       <c r="F369" s="5" t="inlineStr">
         <is>
-          <t>/auth/checkSession</t>
+          <t>/auth/logout</t>
         </is>
       </c>
       <c r="G369" s="5" t="inlineStr">
@@ -14952,7 +14956,7 @@
       </c>
       <c r="H369" s="3" t="inlineStr">
         <is>
-          <t>check_session</t>
+          <t>logout</t>
         </is>
       </c>
     </row>
@@ -14982,7 +14986,7 @@
       </c>
       <c r="F370" s="5" t="inlineStr">
         <is>
-          <t>/auth/checkInstall</t>
+          <t>/auth/checkSession</t>
         </is>
       </c>
       <c r="G370" s="5" t="inlineStr">
@@ -14992,7 +14996,7 @@
       </c>
       <c r="H370" s="3" t="inlineStr">
         <is>
-          <t>checkInstall</t>
+          <t>check_session</t>
         </is>
       </c>
     </row>
@@ -15022,7 +15026,7 @@
       </c>
       <c r="F371" s="5" t="inlineStr">
         <is>
-          <t>/auth/checkRemote/{user}</t>
+          <t>/auth/checkInstall</t>
         </is>
       </c>
       <c r="G371" s="5" t="inlineStr">
@@ -15032,7 +15036,7 @@
       </c>
       <c r="H371" s="3" t="inlineStr">
         <is>
-          <t>check_remoteUser</t>
+          <t>checkInstall</t>
         </is>
       </c>
     </row>
@@ -15052,25 +15056,65 @@
       </c>
       <c r="D372" s="3" t="inlineStr">
         <is>
+          <t>store/auth.js</t>
+        </is>
+      </c>
+      <c r="E372" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="F372" s="5" t="inlineStr">
+        <is>
+          <t>/auth/checkRemote/{user}</t>
+        </is>
+      </c>
+      <c r="G372" s="5" t="inlineStr">
+        <is>
+          <t>routes/auth.py</t>
+        </is>
+      </c>
+      <c r="H372" s="3" t="inlineStr">
+        <is>
+          <t>check_remoteUser</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="3" t="n">
+        <v>360</v>
+      </c>
+      <c r="B373" s="3" t="inlineStr">
+        <is>
+          <t>/signup</t>
+        </is>
+      </c>
+      <c r="C373" s="3" t="inlineStr">
+        <is>
+          <t>pages/main/Signup.vue</t>
+        </is>
+      </c>
+      <c r="D373" s="3" t="inlineStr">
+        <is>
           <t>store/setup.js</t>
         </is>
       </c>
-      <c r="E372" s="4" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="F372" s="5" t="inlineStr">
+      <c r="E373" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="F373" s="5" t="inlineStr">
         <is>
           <t>/setting/checkSettingFile</t>
         </is>
       </c>
-      <c r="G372" s="5" t="inlineStr">
+      <c r="G373" s="5" t="inlineStr">
         <is>
           <t>routes/setting.py</t>
         </is>
       </c>
-      <c r="H372" s="3" t="inlineStr">
+      <c r="H373" s="3" t="inlineStr">
         <is>
           <t>check_setupfile</t>
         </is>
@@ -15091,7 +15135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F212"/>
+  <dimension ref="A1:F213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -15796,22 +15840,22 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>/api/setWave/{channel}/{state}</t>
+          <t>/api/getHarmonicsTrend/{channel}</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>setWave</t>
+          <t>getHarmonicsTrend</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>PowerQ.vue, PowerQ2.vue, PowerQ_New.vue</t>
+          <t>HarmonicsTab.vue (트렌드)</t>
         </is>
       </c>
     </row>
@@ -15831,12 +15875,12 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>/api/getWave/{channel}</t>
+          <t>/api/setWave/{channel}/{state}</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>get_waves</t>
+          <t>setWave</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
@@ -15861,17 +15905,17 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>/api/getDiagnosisDetail/{asset}</t>
+          <t>/api/getWave/{channel}</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>get_diagnosis</t>
+          <t>get_waves</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>DiagnosisTab, TrendTab, Report_Diagnosis, PDFPreview, reportDict.js</t>
+          <t>PowerQ.vue, PowerQ2.vue, PowerQ_New.vue</t>
         </is>
       </c>
     </row>
@@ -15891,17 +15935,17 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>/api/getDiagPQ/{asset}</t>
+          <t>/api/getDiagnosisDetail/{asset}</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>get_diagPQ</t>
+          <t>get_diagnosis</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>DiagnosisTab, TrendTab, Report_PQ, PDFPreview, reportDict.js</t>
+          <t>DiagnosisTab, TrendTab, Report_Diagnosis, PDFPreview, reportDict.js</t>
         </is>
       </c>
     </row>
@@ -15921,17 +15965,17 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>/api/getEvents/{asset}</t>
+          <t>/api/getDiagPQ/{asset}</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>get_events</t>
+          <t>get_diagPQ</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>DiagnosisTab, DashboardCard_Meter_Integrated, Report_Diagnosis</t>
+          <t>DiagnosisTab, TrendTab, Report_PQ, PDFPreview, reportDict.js</t>
         </is>
       </c>
     </row>
@@ -15951,17 +15995,17 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>/api/getFaults/{asset}</t>
+          <t>/api/getEvents/{asset}</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>get_faults</t>
+          <t>get_events</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>DiagnosisTab, Report_Diagnosis</t>
+          <t>DiagnosisTab, DashboardCard_Meter_Integrated, Report_Diagnosis</t>
         </is>
       </c>
     </row>
@@ -15981,17 +16025,17 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>/api/getTrendParameters/{channel}</t>
+          <t>/api/getFaults/{asset}</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>get_trendParams</t>
+          <t>get_faults</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>Trend.vue, TrendTab.vue</t>
+          <t>DiagnosisTab, Report_Diagnosis</t>
         </is>
       </c>
     </row>
@@ -16011,17 +16055,17 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>/api/getParameters/{asset}/{type}</t>
+          <t>/api/getTrendParameters/{channel}</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>get_params</t>
+          <t>get_trendParams</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>Report_Diagnosis, Report_PQ, PDFPreview, reportDict.js</t>
+          <t>Trend.vue, TrendTab.vue</t>
         </is>
       </c>
     </row>
@@ -16041,17 +16085,17 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>/api/getTrendParameters/{asset}/{type}</t>
+          <t>/api/getParameters/{asset}/{type}</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>get_trendParams</t>
+          <t>get_params</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>TrendTab.vue</t>
+          <t>Report_Diagnosis, Report_PQ, PDFPreview, reportDict.js</t>
         </is>
       </c>
     </row>
@@ -16064,24 +16108,24 @@
           <t>/api</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr">
-        <is>
-          <t>POST</t>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>/api/getTrendData</t>
+          <t>/api/getTrendParameters/{asset}/{type}</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>get_trendData</t>
+          <t>get_trendParams</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>TrendTab, Report_Diagnosis, Report_PQ, PDFPreview, reportDict.js</t>
+          <t>TrendTab.vue</t>
         </is>
       </c>
     </row>
@@ -16101,17 +16145,17 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>/api/getTrendbyName</t>
+          <t>/api/getTrendData</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>get_trend_byName</t>
+          <t>get_trendData</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>TrendTab.vue</t>
+          <t>TrendTab, Report_Diagnosis, Report_PQ, PDFPreview, reportDict.js</t>
         </is>
       </c>
     </row>
@@ -16124,24 +16168,24 @@
           <t>/api</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>GET</t>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>/api/getStatus/{asset}/{channel}</t>
+          <t>/api/getTrendbyName</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>getStatus</t>
+          <t>get_trend_byName</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>DashboardCard_New2, DashboardCard_Meter_Integrated</t>
+          <t>TrendTab.vue</t>
         </is>
       </c>
     </row>
@@ -16161,12 +16205,12 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>/api/getPQStatus/{asset}/{channel}</t>
+          <t>/api/getStatus/{asset}/{channel}</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>getPQStatus</t>
+          <t>getStatus</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
@@ -16191,17 +16235,17 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>/api/getDashSatatus/{asset}/{channel}</t>
+          <t>/api/getPQStatus/{asset}/{channel}</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>get_dashStatus</t>
+          <t>getPQStatus</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>DashboardCard_New, DashboardCard_Diagnosis, IntegratedLayout</t>
+          <t>DashboardCard_New2, DashboardCard_Meter_Integrated</t>
         </is>
       </c>
     </row>
@@ -16221,17 +16265,17 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>/api/getRealTimeHarmonics/{ch}/{asset}</t>
+          <t>/api/getDashSatatus/{asset}/{channel}</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>get_realtime_harmonics</t>
+          <t>get_dashStatus</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>PowerQ2.vue, PowerQ_New.vue</t>
+          <t>DashboardCard_New, DashboardCard_Diagnosis, IntegratedLayout</t>
         </is>
       </c>
     </row>
@@ -16251,17 +16295,17 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>/api/getRealTime/{assettype}/{asset}</t>
+          <t>/api/getRealTimeHarmonics/{ch}/{asset}</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>get_realtime</t>
+          <t>get_realtime_harmonics</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>DashboardCard_*, Diagnosis2, Dashboard_Single_Info</t>
+          <t>PowerQ2.vue, PowerQ_New.vue</t>
         </is>
       </c>
     </row>
@@ -16281,17 +16325,17 @@
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>/api/getRealTimeSingle/{ch}/{type}/{asset}</t>
+          <t>/api/getRealTime/{assettype}/{asset}</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>get_realtimesingle</t>
+          <t>get_realtime</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>Dash_InnerSingle.vue</t>
+          <t>DashboardCard_*, Diagnosis2, Dashboard_Single_Info</t>
         </is>
       </c>
     </row>
@@ -16311,17 +16355,17 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>/api/getAsset/{asset}</t>
+          <t>/api/getRealTimeSingle/{ch}/{type}/{asset}</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>get_asset</t>
+          <t>get_realtimesingle</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>Diagnosis2, Dashboard_TransInfo, Dash_InnerEquipment, Report_Info, reportDict.js</t>
+          <t>Dash_InnerSingle.vue</t>
         </is>
       </c>
     </row>
@@ -16341,17 +16385,17 @@
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>/api/getAlarmParms/{channel}</t>
+          <t>/api/getAsset/{asset}</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>get_almParms</t>
+          <t>get_asset</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>EventTable.vue</t>
+          <t>Diagnosis2, Dashboard_TransInfo, Dash_InnerEquipment, Report_Info, reportDict.js</t>
         </is>
       </c>
     </row>
@@ -16371,17 +16415,17 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>/api/getAlarms/{channel}/{page}</t>
+          <t>/api/getAlarmParms/{channel}</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>get_alarms</t>
+          <t>get_almParms</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>EventTab.vue</t>
+          <t>EventTable.vue</t>
         </is>
       </c>
     </row>
@@ -16394,19 +16438,19 @@
           <t>/api</t>
         </is>
       </c>
-      <c r="C46" s="7" t="inlineStr">
-        <is>
-          <t>POST</t>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>/api/getAlarmSearch/{channel}/{page}</t>
+          <t>/api/getAlarms/{channel}/{page}</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>get_alarmSearch</t>
+          <t>get_alarms</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
@@ -16424,19 +16468,19 @@
           <t>/api</t>
         </is>
       </c>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t>GET</t>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>/api/getEventlist/{channel}/{page}</t>
+          <t>/api/getAlarmSearch/{channel}/{page}</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>get_eventlist</t>
+          <t>get_alarmSearch</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
@@ -16454,19 +16498,19 @@
           <t>/api</t>
         </is>
       </c>
-      <c r="C48" s="7" t="inlineStr">
-        <is>
-          <t>POST</t>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>/api/getEventSearch/{channel}/{page}</t>
+          <t>/api/getEventlist/{channel}/{page}</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>get_eventSearch</t>
+          <t>get_eventlist</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
@@ -16484,24 +16528,24 @@
           <t>/api</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
-        <is>
-          <t>GET</t>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>/api/getAlarmStatus/{channel}</t>
+          <t>/api/getEventSearch/{channel}/{page}</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>getAlarmStatus</t>
+          <t>get_eventSearch</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>AlarmStatusTable.vue</t>
+          <t>EventTab.vue</t>
         </is>
       </c>
     </row>
@@ -16521,17 +16565,17 @@
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>/api/getEn50160/{channel}</t>
+          <t>/api/getAlarmStatus/{channel}</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>getEn50160</t>
+          <t>getAlarmStatus</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>ReportComponent, PDFPreview, reportDict.js</t>
+          <t>AlarmStatusTable.vue</t>
         </is>
       </c>
     </row>
@@ -16551,17 +16595,17 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>/api/getITIC/{channel}</t>
+          <t>/api/getEn50160/{channel}</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>get_itic</t>
+          <t>getEn50160</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>ReportComponent, PDFPreview</t>
+          <t>ReportComponent, PDFPreview, reportDict.js</t>
         </is>
       </c>
     </row>
@@ -16581,17 +16625,17 @@
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>/api/getEquipStatus/{channel}</t>
+          <t>/api/getITIC/{channel}</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>get_eqStatus</t>
+          <t>get_itic</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>Dashboard_TransInfo, EquipItem, Dashboard_Single</t>
+          <t>ReportComponent, PDFPreview</t>
         </is>
       </c>
     </row>
@@ -16611,17 +16655,17 @@
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>/api/getAIdata/{channel}</t>
+          <t>/api/getEquipStatus/{channel}</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>get_ai</t>
+          <t>get_eqStatus</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>store/realtime.js</t>
+          <t>Dashboard_TransInfo, EquipItem, Dashboard_Single</t>
         </is>
       </c>
     </row>
@@ -16641,17 +16685,17 @@
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>/api/getMeterRedisNew/{channel}/{mode}</t>
+          <t>/api/getAIdata/{channel}</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>getMeterRedis2</t>
+          <t>get_ai</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>store/realtime.js, DynamicDashboard.vue</t>
+          <t>store/realtime.js</t>
         </is>
       </c>
     </row>
@@ -16671,17 +16715,17 @@
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>/api/getInterval/{mode}/{channel}</t>
+          <t>/api/getMeterRedisNew/{channel}/{mode}</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>get_interval</t>
+          <t>getMeterRedis2</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>Meter.vue, PowerQ2.vue, PowerQ_New.vue</t>
+          <t>store/realtime.js, DynamicDashboard.vue</t>
         </is>
       </c>
     </row>
@@ -16701,17 +16745,17 @@
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>/api/getChData/{channel}</t>
+          <t>/api/getInterval/{mode}/{channel}</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>get_Equip_ChData</t>
+          <t>get_interval</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>PowerQ_New.vue</t>
+          <t>Meter.vue, PowerQ2.vue, PowerQ_New.vue</t>
         </is>
       </c>
     </row>
@@ -16731,17 +16775,17 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>/api/getOnesfromRedis/{channel}/{unbal}</t>
+          <t>/api/getChData/{channel}</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>get_OneSecond</t>
+          <t>get_Equip_ChData</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>Meter.vue</t>
+          <t>PowerQ_New.vue</t>
         </is>
       </c>
     </row>
@@ -16761,12 +16805,12 @@
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>/api/getonemfromRedis/{channel}</t>
+          <t>/api/getOnesfromRedis/{channel}/{unbal}</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>get_onemfromRedis</t>
+          <t>get_OneSecond</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
@@ -16791,12 +16835,12 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>/api/getFifthMfromRedis/{channel}</t>
+          <t>/api/getonemfromRedis/{channel}</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>get_FifthMfromRedis</t>
+          <t>get_onemfromRedis</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
@@ -16821,12 +16865,12 @@
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>/api/getOnehfromRedis/{channel}</t>
+          <t>/api/getFifthMfromRedis/{channel}</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>get_onehRedis</t>
+          <t>get_FifthMfromRedis</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
@@ -16851,17 +16895,17 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>/api/getEnergyRedis/{channel}</t>
+          <t>/api/getOnehfromRedis/{channel}</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>get_consumption_energy</t>
+          <t>get_onehRedis</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>DashboardCard_kwh_realtime, Report_WattHour</t>
+          <t>Meter.vue</t>
         </is>
       </c>
     </row>
@@ -16881,17 +16925,17 @@
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>/api/getSystemStatus</t>
+          <t>/api/getEnergyRedis/{channel}</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>get_service</t>
+          <t>get_consumption_energy</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>Header.vue</t>
+          <t>DashboardCard_kwh_realtime, Report_WattHour</t>
         </is>
       </c>
     </row>
@@ -16904,24 +16948,24 @@
           <t>/api</t>
         </is>
       </c>
-      <c r="C63" s="7" t="inlineStr">
-        <is>
-          <t>POST</t>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>/api/getMeterTrend/{channel}/{save_csv}</t>
+          <t>/api/getSystemStatus</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>getMeterTrendPost</t>
+          <t>get_service</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>TrendTab.vue</t>
+          <t>Header.vue</t>
         </is>
       </c>
     </row>
@@ -16934,19 +16978,19 @@
           <t>/api</t>
         </is>
       </c>
-      <c r="C64" s="4" t="inlineStr">
-        <is>
-          <t>GET</t>
+      <c r="C64" s="7" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>/api/getEnergyTrend/{channel}</t>
+          <t>/api/getMeterTrend/{channel}/{save_csv}</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>getEnergyTrend</t>
+          <t>getMeterTrendPost</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
@@ -16971,17 +17015,17 @@
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>/api/getHourlyEnergyData/{channel}</t>
+          <t>/api/getEnergyTrend/{channel}</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>get_hourEnergy</t>
+          <t>getEnergyTrend</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>DashboardCard_kwh_realtime, reportDict.js</t>
+          <t>TrendTab.vue</t>
         </is>
       </c>
     </row>
@@ -17001,17 +17045,17 @@
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>/api/getDailyEnergyData/{channel}</t>
+          <t>/api/getHourlyEnergyData/{channel}</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>get_dailyEnergy</t>
+          <t>get_hourEnergy</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>reportDict.js</t>
+          <t>DashboardCard_kwh_realtime, reportDict.js</t>
         </is>
       </c>
     </row>
@@ -17031,12 +17075,12 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>/api/getMonthlyEnergyData/{channel}</t>
+          <t>/api/getDailyEnergyData/{channel}</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>get_monthlyEnergy</t>
+          <t>get_dailyEnergy</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
@@ -17061,12 +17105,12 @@
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>/api/getLoadFactorCalculated/{channel}</t>
+          <t>/api/getMonthlyEnergyData/{channel}</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>get_load_factor_calculated</t>
+          <t>get_monthlyEnergy</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
@@ -17091,12 +17135,12 @@
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>/api/getWeeklyLoadFactorData/{channel}</t>
+          <t>/api/getLoadFactorCalculated/{channel}</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>get_weekly_load_factor_data</t>
+          <t>get_load_factor_calculated</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
@@ -17121,12 +17165,12 @@
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>/api/getHeatmapLoadFactorData/{channel}</t>
+          <t>/api/getWeeklyLoadFactorData/{channel}</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>get_heatmap_load_factor_data</t>
+          <t>get_weekly_load_factor_data</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
@@ -17151,17 +17195,17 @@
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>/api/download/{mode}/{lang}</t>
+          <t>/api/getHeatmapLoadFactorData/{channel}</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>get_deviceDoc</t>
+          <t>get_heatmap_load_factor_data</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>DropdownHelp.vue</t>
+          <t>reportDict.js</t>
         </is>
       </c>
     </row>
@@ -17181,17 +17225,17 @@
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>/api/getTransRedis/{channel}</t>
+          <t>/api/download/{mode}/{lang}</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>getTransRedis</t>
-        </is>
-      </c>
-      <c r="F72" s="16" t="inlineStr">
-        <is>
-          <t>(프론트엔드 미사용)</t>
+          <t>get_deviceDoc</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>DropdownHelp.vue</t>
         </is>
       </c>
     </row>
@@ -17211,12 +17255,12 @@
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>/api/getAllMeterRedisNew/{channel}</t>
+          <t>/api/getTransRedis/{channel}</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>get_all_meter_redis</t>
+          <t>getTransRedis</t>
         </is>
       </c>
       <c r="F73" s="16" t="inlineStr">
@@ -17241,12 +17285,12 @@
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>/api/getEnergy/{channel}</t>
+          <t>/api/getAllMeterRedisNew/{channel}</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>get_energy</t>
+          <t>get_all_meter_redis</t>
         </is>
       </c>
       <c r="F74" s="16" t="inlineStr">
@@ -17271,12 +17315,12 @@
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>/api/getLoadFactorData/{channel}</t>
+          <t>/api/getEnergy/{channel}</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>get_load_factor_data</t>
+          <t>get_energy</t>
         </is>
       </c>
       <c r="F75" s="16" t="inlineStr">
@@ -17301,12 +17345,12 @@
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>/api/getDiagnosisCached/{ch}/{asset}</t>
+          <t>/api/getLoadFactorData/{channel}</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>get_diagnosis_cached</t>
+          <t>get_load_factor_data</t>
         </is>
       </c>
       <c r="F76" s="16" t="inlineStr">
@@ -17331,12 +17375,12 @@
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>/api/getTrendTreePQ/{asset}</t>
+          <t>/api/getDiagnosisCached/{ch}/{asset}</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>get_trend_tree_pq</t>
+          <t>get_diagnosis_cached</t>
         </is>
       </c>
       <c r="F77" s="16" t="inlineStr">
@@ -17361,12 +17405,12 @@
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>/api/getTrendTreeDiagnosis/{asset}</t>
+          <t>/api/getTrendTreePQ/{asset}</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>get_trend_tree_diagnosis</t>
+          <t>get_trend_tree_pq</t>
         </is>
       </c>
       <c r="F78" s="16" t="inlineStr">
@@ -17386,22 +17430,22 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>/api/downloadTrendCsv/{channel}</t>
+          <t>/api/getTrendTreeDiagnosis/{asset}</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>downloadTrendCsv</t>
+          <t>get_trend_tree_diagnosis</t>
         </is>
       </c>
       <c r="F79" s="16" t="inlineStr">
         <is>
-          <t>ServicePanel_New.vue</t>
+          <t>(프론트엔드 미사용)</t>
         </is>
       </c>
     </row>
@@ -17416,22 +17460,22 @@
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>/api/getDemandTrend/{channel}</t>
+          <t>/api/downloadTrendCsv/{channel}</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>getDemandTrend</t>
+          <t>downloadTrendCsv</t>
         </is>
       </c>
       <c r="F80" s="16" t="inlineStr">
         <is>
-          <t>TrendTab.vue</t>
+          <t>ServicePanel_New.vue</t>
         </is>
       </c>
     </row>
@@ -17451,17 +17495,17 @@
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>/api/getDiagnosis/{asset}</t>
+          <t>/api/getDemandTrend/{channel}</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>get_diagnosis</t>
+          <t>getDemandTrend</t>
         </is>
       </c>
       <c r="F81" s="16" t="inlineStr">
         <is>
-          <t>DiagnosisTab.vue, DiagnosisTab_Bands.vue, DiagnosisTab_Bands_Legacy.vue, DiagnosisTab_Chart.vue, DiagnosisTab_New.vue, PDFPreview.vue, Report_Diagnosis.vue, Report_Diagnosis_accordian.vue, TrendTab.vue, reportDict.js</t>
+          <t>TrendTab.vue</t>
         </is>
       </c>
     </row>
@@ -17481,17 +17525,17 @@
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>/api/getModuleStatus/{channel}</t>
+          <t>/api/getDiagnosis/{asset}</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>getMDStatus</t>
+          <t>get_diagnosis</t>
         </is>
       </c>
       <c r="F82" s="16" t="inlineStr">
         <is>
-          <t>DashboardCard_Diagnosis.vue, DashboardCard_Meter_Integrated_total2.vue, DashboardCard_New.vue, DualMeasCard_Diagnosis.vue, DualMeasCard_Diagnosis_v2.vue, SingleMeasCard_Diagnosis.vue</t>
+          <t>DiagnosisTab.vue, DiagnosisTab_Bands.vue, DiagnosisTab_Bands_Legacy.vue, DiagnosisTab_Chart.vue, DiagnosisTab_New.vue, PDFPreview.vue, Report_Diagnosis.vue, Report_Diagnosis_accordian.vue, TrendTab.vue, reportDict.js</t>
         </is>
       </c>
     </row>
@@ -17511,17 +17555,17 @@
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>/api/getRealTimeTHD/{asset}</t>
+          <t>/api/getModuleStatus/{channel}</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>get_realtime</t>
+          <t>getMDStatus</t>
         </is>
       </c>
       <c r="F83" s="16" t="inlineStr">
         <is>
-          <t>MeterTHD_VFD.vue</t>
+          <t>DashboardCard_Diagnosis.vue, DashboardCard_Meter_Integrated_total2.vue, DashboardCard_New.vue, DualMeasCard_Diagnosis.vue, DualMeasCard_Diagnosis_v2.vue, SingleMeasCard_Diagnosis.vue</t>
         </is>
       </c>
     </row>
@@ -17541,54 +17585,54 @@
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
+          <t>/api/getRealTimeTHD/{asset}</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>get_realtime</t>
+        </is>
+      </c>
+      <c r="F84" s="16" t="inlineStr">
+        <is>
+          <t>MeterTHD_VFD.vue</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>/api</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
           <t>/api/relearn/{asset}</t>
         </is>
       </c>
-      <c r="E84" s="3" t="inlineStr">
+      <c r="E85" s="3" t="inlineStr">
         <is>
           <t>relearn_asset</t>
         </is>
       </c>
-      <c r="F84" s="16" t="inlineStr">
+      <c r="F85" s="16" t="inlineStr">
         <is>
           <t>AssetCard.vue</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="15" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="15" t="inlineStr">
         <is>
           <t>/setting (settingRouter - routes/setting.py)</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="3" t="n">
-        <v>81</v>
-      </c>
-      <c r="B86" s="11" t="inlineStr">
-        <is>
-          <t>/setting</t>
-        </is>
-      </c>
-      <c r="C86" s="4" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="D86" s="3" t="inlineStr">
-        <is>
-          <t>/setting/getMac</t>
-        </is>
-      </c>
-      <c r="E86" s="3" t="inlineStr">
-        <is>
-          <t>getMacAddr</t>
-        </is>
-      </c>
-      <c r="F86" s="16" t="inlineStr">
-        <is>
-          <t>(프론트엔드 미사용)</t>
         </is>
       </c>
     </row>
@@ -17608,12 +17652,12 @@
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>/setting/checkInitDB</t>
+          <t>/setting/getMac</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>checkInitDB</t>
+          <t>getMacAddr</t>
         </is>
       </c>
       <c r="F87" s="16" t="inlineStr">
@@ -17638,17 +17682,17 @@
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>/setting/checkInfluxStatus</t>
+          <t>/setting/checkInitDB</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>check_influxStatus</t>
-        </is>
-      </c>
-      <c r="F88" s="3" t="inlineStr">
-        <is>
-          <t>ServicePanel.vue, ServicePanel_New.vue</t>
+          <t>checkInitDB</t>
+        </is>
+      </c>
+      <c r="F88" s="16" t="inlineStr">
+        <is>
+          <t>(프론트엔드 미사용)</t>
         </is>
       </c>
     </row>
@@ -17668,17 +17712,17 @@
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>/setting/initDB</t>
+          <t>/setting/checkInfluxStatus</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>initInflux</t>
+          <t>check_influxStatus</t>
         </is>
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>ServicePanel, CommandItem.vue</t>
+          <t>ServicePanel.vue, ServicePanel_New.vue</t>
         </is>
       </c>
     </row>
@@ -17698,17 +17742,17 @@
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>/setting/initInfluxCLI</t>
+          <t>/setting/initDB</t>
         </is>
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>init_influxcli</t>
+          <t>initInflux</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>ServicePanel.vue</t>
+          <t>ServicePanel, CommandItem.vue</t>
         </is>
       </c>
     </row>
@@ -17728,17 +17772,17 @@
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>/setting/setup-downsampling</t>
+          <t>/setting/initInfluxCLI</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>setup_downsampling_endpoint</t>
+          <t>init_influxcli</t>
         </is>
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>ServicePanel.vue, ServicePanel_New.vue</t>
+          <t>ServicePanel.vue</t>
         </is>
       </c>
     </row>
@@ -17758,12 +17802,12 @@
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>/setting/initDB/status</t>
+          <t>/setting/setup-downsampling</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>get_init_status</t>
+          <t>setup_downsampling_endpoint</t>
         </is>
       </c>
       <c r="F92" s="3" t="inlineStr">
@@ -17788,17 +17832,17 @@
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>/setting/checkSettingFile</t>
+          <t>/setting/initDB/status</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>check_setupfile</t>
+          <t>get_init_status</t>
         </is>
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>store/setup.js</t>
+          <t>ServicePanel.vue, ServicePanel_New.vue</t>
         </is>
       </c>
     </row>
@@ -17818,17 +17862,17 @@
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>/setting/getSetting</t>
+          <t>/setting/checkSettingFile</t>
         </is>
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>get_setting</t>
+          <t>check_setupfile</t>
         </is>
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>SettingNew, OnBoardingModal, OnboardModal</t>
+          <t>store/setup.js</t>
         </is>
       </c>
     </row>
@@ -17848,17 +17892,17 @@
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>/setting/getSettingData/{channel}</t>
+          <t>/setting/getSetting</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>getDatafromSetting</t>
+          <t>get_setting</t>
         </is>
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>Setting.vue, SettingNew.vue, PlansPanel.vue</t>
+          <t>SettingNew, OnBoardingModal, OnboardModal</t>
         </is>
       </c>
     </row>
@@ -17878,17 +17922,17 @@
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>/setting/Reset</t>
+          <t>/setting/getSettingData/{channel}</t>
         </is>
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>reset</t>
+          <t>getDatafromSetting</t>
         </is>
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>SettingNew, MasterDashboard, CommandItem</t>
+          <t>Setting.vue, SettingNew.vue, PlansPanel.vue</t>
         </is>
       </c>
     </row>
@@ -17908,17 +17952,17 @@
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>/setting/ResetAll</t>
+          <t>/setting/Reset</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>resetAll</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>ServicePanel, CommandItem</t>
+          <t>SettingNew, MasterDashboard, CommandItem</t>
         </is>
       </c>
     </row>
@@ -17938,17 +17982,17 @@
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>/setting/getDiagnosisSetting</t>
+          <t>/setting/ResetAll</t>
         </is>
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>get_diagnosissetting</t>
+          <t>resetAll</t>
         </is>
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>SettingNew.vue, SaveProgressModal.vue</t>
+          <t>ServicePanel, CommandItem</t>
         </is>
       </c>
     </row>
@@ -17968,17 +18012,17 @@
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>/setting/getDiagnosisProfile</t>
+          <t>/setting/getDiagnosisSetting</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>get_diagnosisprofile</t>
+          <t>get_diagnosissetting</t>
         </is>
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>SettingNew, General_diagnosisCard</t>
+          <t>SettingNew.vue, SaveProgressModal.vue</t>
         </is>
       </c>
     </row>
@@ -17991,24 +18035,24 @@
           <t>/setting</t>
         </is>
       </c>
-      <c r="C100" s="7" t="inlineStr">
-        <is>
-          <t>POST</t>
+      <c r="C100" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>/setting/setDiagnosisSetting</t>
+          <t>/setting/getDiagnosisProfile</t>
         </is>
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>set_diagnosissetting</t>
+          <t>get_diagnosisprofile</t>
         </is>
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>Setting, PlansPanel, SaveProgressModal</t>
+          <t>SettingNew, General_diagnosisCard</t>
         </is>
       </c>
     </row>
@@ -18028,12 +18072,12 @@
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>/setting/setDiagnosisProfile</t>
+          <t>/setting/setDiagnosisSetting</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>set_diagnosisprofile</t>
+          <t>set_diagnosissetting</t>
         </is>
       </c>
       <c r="F101" s="3" t="inlineStr">
@@ -18051,24 +18095,24 @@
           <t>/setting</t>
         </is>
       </c>
-      <c r="C102" s="4" t="inlineStr">
-        <is>
-          <t>GET</t>
+      <c r="C102" s="7" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>/setting/getAssetTypes</t>
+          <t>/setting/setDiagnosisProfile</t>
         </is>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>get_assetTypes</t>
+          <t>set_diagnosisprofile</t>
         </is>
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>AssetCard.vue</t>
+          <t>Setting, PlansPanel, SaveProgressModal</t>
         </is>
       </c>
     </row>
@@ -18088,12 +18132,12 @@
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>/setting/getAssetList</t>
+          <t>/setting/getAssetTypes</t>
         </is>
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>get_assetlist</t>
+          <t>get_assetTypes</t>
         </is>
       </c>
       <c r="F103" s="3" t="inlineStr">
@@ -18111,24 +18155,24 @@
           <t>/setting</t>
         </is>
       </c>
-      <c r="C104" s="7" t="inlineStr">
-        <is>
-          <t>POST</t>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>/setting/upload</t>
+          <t>/setting/getAssetList</t>
         </is>
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>upload_file</t>
+          <t>get_assetlist</t>
         </is>
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>Setting, PlansPanel, CommandItem</t>
+          <t>AssetCard.vue</t>
         </is>
       </c>
     </row>
@@ -18141,24 +18185,24 @@
           <t>/setting</t>
         </is>
       </c>
-      <c r="C105" s="4" t="inlineStr">
-        <is>
-          <t>GET</t>
+      <c r="C105" s="7" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>/setting/checkBearing</t>
+          <t>/setting/upload</t>
         </is>
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>load_bearings_from_db</t>
+          <t>upload_file</t>
         </is>
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>NameplateCard.vue</t>
+          <t>Setting, PlansPanel, CommandItem</t>
         </is>
       </c>
     </row>
@@ -18171,19 +18215,19 @@
           <t>/setting</t>
         </is>
       </c>
-      <c r="C106" s="7" t="inlineStr">
-        <is>
-          <t>POST</t>
+      <c r="C106" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>/setting/uploadBearing</t>
+          <t>/setting/checkBearing</t>
         </is>
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>upload_bearing_to_db</t>
+          <t>load_bearings_from_db</t>
         </is>
       </c>
       <c r="F106" s="3" t="inlineStr">
@@ -18201,24 +18245,24 @@
           <t>/setting</t>
         </is>
       </c>
-      <c r="C107" s="4" t="inlineStr">
-        <is>
-          <t>GET</t>
+      <c r="C107" s="7" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>/setting/download</t>
+          <t>/setting/uploadBearing</t>
         </is>
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>download_setting</t>
+          <t>upload_bearing_to_db</t>
         </is>
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>Setting, CommandItem</t>
+          <t>NameplateCard.vue</t>
         </is>
       </c>
     </row>
@@ -18231,24 +18275,24 @@
           <t>/setting</t>
         </is>
       </c>
-      <c r="C108" s="7" t="inlineStr">
-        <is>
-          <t>POST</t>
+      <c r="C108" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>/setting/createAsset</t>
+          <t>/setting/download</t>
         </is>
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
-          <t>createAsset</t>
+          <t>download_setting</t>
         </is>
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>AssetCard.vue</t>
+          <t>Setting, CommandItem</t>
         </is>
       </c>
     </row>
@@ -18268,12 +18312,12 @@
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>/setting/modifyAsset</t>
+          <t>/setting/createAsset</t>
         </is>
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>modifyAsset</t>
+          <t>createAsset</t>
         </is>
       </c>
       <c r="F109" s="3" t="inlineStr">
@@ -18291,19 +18335,19 @@
           <t>/setting</t>
         </is>
       </c>
-      <c r="C110" s="4" t="inlineStr">
-        <is>
-          <t>GET</t>
+      <c r="C110" s="7" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>/setting/deleteAsset/{asset}</t>
+          <t>/setting/modifyAsset</t>
         </is>
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>deleteAsset</t>
+          <t>modifyAsset</t>
         </is>
       </c>
       <c r="F110" s="3" t="inlineStr">
@@ -18328,12 +18372,12 @@
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>/setting/unregisterAsset/{ch}/{asset}</t>
+          <t>/setting/deleteAsset/{asset}</t>
         </is>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>unreg_Asset</t>
+          <t>deleteAsset</t>
         </is>
       </c>
       <c r="F111" s="3" t="inlineStr">
@@ -18358,12 +18402,12 @@
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>/setting/registerAsset/{ch}/{name}/{type}</t>
+          <t>/setting/unregisterAsset/{ch}/{asset}</t>
         </is>
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>reg_Asset</t>
+          <t>unreg_Asset</t>
         </is>
       </c>
       <c r="F112" s="3" t="inlineStr">
@@ -18381,24 +18425,24 @@
           <t>/setting</t>
         </is>
       </c>
-      <c r="C113" s="7" t="inlineStr">
-        <is>
-          <t>POST</t>
+      <c r="C113" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>/setting/savefile/{channel}</t>
+          <t>/setting/registerAsset/{ch}/{name}/{type}</t>
         </is>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>saveSetting</t>
+          <t>reg_Asset</t>
         </is>
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>Setting.vue</t>
+          <t>AssetCard.vue</t>
         </is>
       </c>
     </row>
@@ -18418,17 +18462,17 @@
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>/setting/savefileNew</t>
+          <t>/setting/savefile/{channel}</t>
         </is>
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>saveSetting2</t>
+          <t>saveSetting</t>
         </is>
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>SettingNew_back, SaveProgressModal</t>
+          <t>Setting.vue</t>
         </is>
       </c>
     </row>
@@ -18441,24 +18485,24 @@
           <t>/setting</t>
         </is>
       </c>
-      <c r="C115" s="4" t="inlineStr">
-        <is>
-          <t>GET</t>
+      <c r="C115" s="7" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>/setting/apply</t>
+          <t>/setting/savefileNew</t>
         </is>
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>apply</t>
+          <t>saveSetting2</t>
         </is>
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>OnBoardingModal2.vue</t>
+          <t>SettingNew_back, SaveProgressModal</t>
         </is>
       </c>
     </row>
@@ -18478,12 +18522,12 @@
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>/setting/checkCommision/{asset}</t>
+          <t>/setting/apply</t>
         </is>
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>check_comm</t>
+          <t>apply</t>
         </is>
       </c>
       <c r="F116" s="3" t="inlineStr">
@@ -18508,17 +18552,17 @@
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>/setting/checkSmart</t>
+          <t>/setting/checkCommision/{asset}</t>
         </is>
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>check_smart</t>
+          <t>check_comm</t>
         </is>
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>Setting, SettingNew</t>
+          <t>OnBoardingModal2.vue</t>
         </is>
       </c>
     </row>
@@ -18538,12 +18582,12 @@
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
-          <t>/setting/manageSmart/{mode}</t>
+          <t>/setting/checkSmart</t>
         </is>
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
-          <t>manage_smart</t>
+          <t>check_smart</t>
         </is>
       </c>
       <c r="F118" s="3" t="inlineStr">
@@ -18568,17 +18612,17 @@
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t>/setting/restartasset</t>
+          <t>/setting/manageSmart/{mode}</t>
         </is>
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>restartasset</t>
+          <t>manage_smart</t>
         </is>
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>Setting, SettingNew, ChannelPanel</t>
+          <t>Setting, SettingNew</t>
         </is>
       </c>
     </row>
@@ -18598,17 +18642,17 @@
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t>/setting/restartdevice</t>
+          <t>/setting/restartasset</t>
         </is>
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>restartdevice</t>
+          <t>restartasset</t>
         </is>
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>OnBoardingModal, OnBoardingModal2</t>
+          <t>Setting, SettingNew, ChannelPanel</t>
         </is>
       </c>
     </row>
@@ -18621,24 +18665,24 @@
           <t>/setting</t>
         </is>
       </c>
-      <c r="C121" s="7" t="inlineStr">
-        <is>
-          <t>POST</t>
+      <c r="C121" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>/setting/restoreSetting</t>
+          <t>/setting/restartdevice</t>
         </is>
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>restore_setting</t>
+          <t>restartdevice</t>
         </is>
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>CommandItem.vue</t>
+          <t>OnBoardingModal, OnBoardingModal2</t>
         </is>
       </c>
     </row>
@@ -18651,24 +18695,24 @@
           <t>/setting</t>
         </is>
       </c>
-      <c r="C122" s="4" t="inlineStr">
-        <is>
-          <t>GET</t>
+      <c r="C122" s="7" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
-          <t>/setting/getAssetConfig/{asset}</t>
+          <t>/setting/restoreSetting</t>
         </is>
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>get_assetconfig</t>
+          <t>restore_setting</t>
         </is>
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t>ChannelPanel.vue</t>
+          <t>CommandItem.vue</t>
         </is>
       </c>
     </row>
@@ -18681,24 +18725,24 @@
           <t>/setting</t>
         </is>
       </c>
-      <c r="C123" s="7" t="inlineStr">
-        <is>
-          <t>POST</t>
+      <c r="C123" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>/setting/checkAssetConfig/{asset}</t>
+          <t>/setting/getAssetConfig/{asset}</t>
         </is>
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>check_assetconfig</t>
+          <t>get_assetconfig</t>
         </is>
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t>Setting, ChannelPanel, SaveProgressModal</t>
+          <t>ChannelPanel.vue</t>
         </is>
       </c>
     </row>
@@ -18718,17 +18762,17 @@
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>/setting/setAssetConfig/{asset}</t>
+          <t>/setting/checkAssetConfig/{asset}</t>
         </is>
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>set_assetconfig</t>
+          <t>check_assetconfig</t>
         </is>
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>Setting, ChannelPanel, NameplateCard, SaveProgressModal</t>
+          <t>Setting, ChannelPanel, SaveProgressModal</t>
         </is>
       </c>
     </row>
@@ -18741,24 +18785,24 @@
           <t>/setting</t>
         </is>
       </c>
-      <c r="C125" s="4" t="inlineStr">
-        <is>
-          <t>GET</t>
+      <c r="C125" s="7" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>/setting/getAssetParams/{asset}</t>
+          <t>/setting/setAssetConfig/{asset}</t>
         </is>
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>get_assetParams</t>
+          <t>set_assetconfig</t>
         </is>
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>ChannelPanel.vue</t>
+          <t>Setting, ChannelPanel, NameplateCard, SaveProgressModal</t>
         </is>
       </c>
     </row>
@@ -18771,24 +18815,24 @@
           <t>/setting</t>
         </is>
       </c>
-      <c r="C126" s="7" t="inlineStr">
-        <is>
-          <t>POST</t>
+      <c r="C126" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t>/setting/setAssetParams/{asset}</t>
+          <t>/setting/getAssetParams/{asset}</t>
         </is>
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>set_assetParams</t>
+          <t>get_assetParams</t>
         </is>
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>Setting, ChannelPanel, SaveProgressModal</t>
+          <t>ChannelPanel.vue</t>
         </is>
       </c>
     </row>
@@ -18801,24 +18845,24 @@
           <t>/setting</t>
         </is>
       </c>
-      <c r="C127" s="4" t="inlineStr">
-        <is>
-          <t>GET</t>
+      <c r="C127" s="7" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t>/setting/test/{channel}/{asset}</t>
+          <t>/setting/setAssetParams/{asset}</t>
         </is>
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>test_asset</t>
+          <t>set_assetParams</t>
         </is>
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>ChannelPanel, OnBoardingModal, OnBoardingModal2</t>
+          <t>Setting, ChannelPanel, SaveProgressModal</t>
         </is>
       </c>
     </row>
@@ -18838,17 +18882,17 @@
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t>/setting/testwave/{asset}</t>
+          <t>/setting/test/{channel}/{asset}</t>
         </is>
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>test_wave</t>
+          <t>test_asset</t>
         </is>
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>OnBoardingModal, OnBoardingModal2</t>
+          <t>ChannelPanel, OnBoardingModal, OnBoardingModal2</t>
         </is>
       </c>
     </row>
@@ -18868,17 +18912,17 @@
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>/setting/checkSmartStatus</t>
+          <t>/setting/testwave/{asset}</t>
         </is>
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>check_SmartStatus</t>
+          <t>test_wave</t>
         </is>
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>ServicePanel.vue</t>
+          <t>OnBoardingModal, OnBoardingModal2</t>
         </is>
       </c>
     </row>
@@ -18891,24 +18935,24 @@
           <t>/setting</t>
         </is>
       </c>
-      <c r="C130" s="7" t="inlineStr">
-        <is>
-          <t>POST</t>
+      <c r="C130" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>/setting/uploadCerts</t>
+          <t>/setting/checkSmartStatus</t>
         </is>
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>upload_certs</t>
+          <t>check_SmartStatus</t>
         </is>
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>PlansPanel.vue</t>
+          <t>ServicePanel.vue</t>
         </is>
       </c>
     </row>
@@ -18921,19 +18965,19 @@
           <t>/setting</t>
         </is>
       </c>
-      <c r="C131" s="4" t="inlineStr">
-        <is>
-          <t>GET</t>
+      <c r="C131" s="7" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t>/setting/listCerts</t>
+          <t>/setting/uploadCerts</t>
         </is>
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>list_certs</t>
+          <t>upload_certs</t>
         </is>
       </c>
       <c r="F131" s="3" t="inlineStr">
@@ -18951,19 +18995,19 @@
           <t>/setting</t>
         </is>
       </c>
-      <c r="C132" s="13" t="inlineStr">
-        <is>
-          <t>DELETE</t>
+      <c r="C132" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>/setting/deleteCert/{filename}</t>
+          <t>/setting/listCerts</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>delete_cert</t>
+          <t>list_certs</t>
         </is>
       </c>
       <c r="F132" s="3" t="inlineStr">
@@ -18981,24 +19025,24 @@
           <t>/setting</t>
         </is>
       </c>
-      <c r="C133" s="4" t="inlineStr">
-        <is>
-          <t>GET</t>
+      <c r="C133" s="13" t="inlineStr">
+        <is>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>/setting/checkMQTT</t>
+          <t>/setting/deleteCert/{filename}</t>
         </is>
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>check_mqtt</t>
+          <t>delete_cert</t>
         </is>
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>SettingNew.vue</t>
+          <t>PlansPanel.vue</t>
         </is>
       </c>
     </row>
@@ -19018,17 +19062,17 @@
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>/setting/checkFrp</t>
+          <t>/setting/checkMQTT</t>
         </is>
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>check_frp</t>
+          <t>check_mqtt</t>
         </is>
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>ServicePanel.vue, ServicePanel_New.vue</t>
+          <t>SettingNew.vue</t>
         </is>
       </c>
     </row>
@@ -19048,17 +19092,17 @@
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>/setting/SysCheck</t>
+          <t>/setting/checkFrp</t>
         </is>
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>check_sysStatus</t>
+          <t>check_frp</t>
         </is>
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>CommandPanel, ServicePanel</t>
+          <t>ServicePanel.vue, ServicePanel_New.vue</t>
         </is>
       </c>
     </row>
@@ -19078,17 +19122,17 @@
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
-          <t>/setting/SysService/{cmd}/{item}</t>
+          <t>/setting/SysCheck</t>
         </is>
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>control_service</t>
+          <t>check_sysStatus</t>
         </is>
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>Setting, CommandItem, ServiceCard</t>
+          <t>CommandPanel, ServicePanel</t>
         </is>
       </c>
     </row>
@@ -19101,24 +19145,24 @@
           <t>/setting</t>
         </is>
       </c>
-      <c r="C137" s="7" t="inlineStr">
-        <is>
-          <t>POST</t>
+      <c r="C137" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr">
         <is>
-          <t>/setting/command</t>
+          <t>/setting/SysService/{cmd}/{item}</t>
         </is>
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>push_command_left</t>
+          <t>control_service</t>
         </is>
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>CommandItem.vue</t>
+          <t>Setting, CommandItem, ServiceCard</t>
         </is>
       </c>
     </row>
@@ -19131,24 +19175,24 @@
           <t>/setting</t>
         </is>
       </c>
-      <c r="C138" s="4" t="inlineStr">
-        <is>
-          <t>GET</t>
+      <c r="C138" s="7" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>/setting/HarmTrigger/{channel}</t>
+          <t>/setting/command</t>
         </is>
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>set_harmTrigger</t>
+          <t>push_command_left</t>
         </is>
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>PowerQ2.vue, PowerQ_New.vue</t>
+          <t>CommandItem.vue</t>
         </is>
       </c>
     </row>
@@ -19168,17 +19212,17 @@
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t>/setting/trigger</t>
+          <t>/setting/HarmTrigger/{channel}</t>
         </is>
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>trigger_waveform</t>
+          <t>set_harmTrigger</t>
         </is>
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>OnBoardingModal2.vue</t>
+          <t>PowerQ2.vue, PowerQ_New.vue</t>
         </is>
       </c>
     </row>
@@ -19198,17 +19242,17 @@
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
-          <t>/setting/getMode</t>
+          <t>/setting/trigger</t>
         </is>
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>get_sysMode</t>
-        </is>
-      </c>
-      <c r="F140" s="16" t="inlineStr">
-        <is>
-          <t>(프론트엔드 미사용)</t>
+          <t>trigger_waveform</t>
+        </is>
+      </c>
+      <c r="F140" s="3" t="inlineStr">
+        <is>
+          <t>OnBoardingModal2.vue</t>
         </is>
       </c>
     </row>
@@ -19228,17 +19272,17 @@
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
-          <t>/setting/updateSmartSystem/{mode}</t>
+          <t>/setting/getMode</t>
         </is>
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>update_smartsystem</t>
-        </is>
-      </c>
-      <c r="F141" s="3" t="inlineStr">
-        <is>
-          <t>CommandPanel (config)</t>
+          <t>get_sysMode</t>
+        </is>
+      </c>
+      <c r="F141" s="16" t="inlineStr">
+        <is>
+          <t>(프론트엔드 미사용)</t>
         </is>
       </c>
     </row>
@@ -19251,24 +19295,24 @@
           <t>/setting</t>
         </is>
       </c>
-      <c r="C142" s="7" t="inlineStr">
-        <is>
-          <t>POST</t>
+      <c r="C142" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>/setting/setDefaultIP</t>
+          <t>/setting/updateSmartSystem/{mode}</t>
         </is>
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>set_defaultIP</t>
+          <t>update_smartsystem</t>
         </is>
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>ServicePanel.vue, ServicePanel_New.vue</t>
+          <t>CommandPanel (config)</t>
         </is>
       </c>
     </row>
@@ -19281,24 +19325,24 @@
           <t>/setting</t>
         </is>
       </c>
-      <c r="C143" s="4" t="inlineStr">
-        <is>
-          <t>GET</t>
+      <c r="C143" s="7" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>/setting/backup/download/{backup_type}</t>
+          <t>/setting/setDefaultIP</t>
         </is>
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>download_backup</t>
-        </is>
-      </c>
-      <c r="F143" s="16" t="inlineStr">
-        <is>
-          <t>(프론트엔드 미사용)</t>
+          <t>set_defaultIP</t>
+        </is>
+      </c>
+      <c r="F143" s="3" t="inlineStr">
+        <is>
+          <t>ServicePanel.vue, ServicePanel_New.vue</t>
         </is>
       </c>
     </row>
@@ -19318,12 +19362,12 @@
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>/setting/check-downsampling</t>
+          <t>/setting/backup/download/{backup_type}</t>
         </is>
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>check_downsampling_status</t>
+          <t>download_backup</t>
         </is>
       </c>
       <c r="F144" s="16" t="inlineStr">
@@ -19348,12 +19392,12 @@
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>/setting/restartCore</t>
+          <t>/setting/check-downsampling</t>
         </is>
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>restart_core</t>
+          <t>check_downsampling_status</t>
         </is>
       </c>
       <c r="F145" s="16" t="inlineStr">
@@ -19378,12 +19422,12 @@
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>/setting/ServiceStatus</t>
+          <t>/setting/restartCore</t>
         </is>
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>check_allservice</t>
+          <t>restart_core</t>
         </is>
       </c>
       <c r="F146" s="16" t="inlineStr">
@@ -19396,7 +19440,7 @@
       <c r="A147" s="3" t="n">
         <v>142</v>
       </c>
-      <c r="B147" s="6" t="inlineStr">
+      <c r="B147" s="11" t="inlineStr">
         <is>
           <t>/setting</t>
         </is>
@@ -19408,17 +19452,17 @@
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>/setting/applyNetwork</t>
+          <t>/setting/ServiceStatus</t>
         </is>
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>apply_network</t>
+          <t>check_allservice</t>
         </is>
       </c>
       <c r="F147" s="16" t="inlineStr">
         <is>
-          <t>SettingNew.vue</t>
+          <t>(프론트엔드 미사용)</t>
         </is>
       </c>
     </row>
@@ -19438,17 +19482,17 @@
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>/setting/backup/file/{task_id}</t>
+          <t>/setting/applyNetwork</t>
         </is>
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>download_backup_file</t>
+          <t>apply_network</t>
         </is>
       </c>
       <c r="F148" s="16" t="inlineStr">
         <is>
-          <t>CommandPanel.vue</t>
+          <t>SettingNew.vue</t>
         </is>
       </c>
     </row>
@@ -19468,17 +19512,17 @@
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t>/setting/backup/parquet/report/download</t>
+          <t>/setting/backup/file/{task_id}</t>
         </is>
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>download_report_parquet</t>
+          <t>download_backup_file</t>
         </is>
       </c>
       <c r="F149" s="16" t="inlineStr">
         <is>
-          <t>ServicePanel_New.vue</t>
+          <t>CommandPanel.vue</t>
         </is>
       </c>
     </row>
@@ -19498,12 +19542,12 @@
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
-          <t>/setting/backup/parquet/report/download-all</t>
+          <t>/setting/backup/parquet/report/download</t>
         </is>
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>download_all_reports</t>
+          <t>download_report_parquet</t>
         </is>
       </c>
       <c r="F150" s="16" t="inlineStr">
@@ -19528,12 +19572,12 @@
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
-          <t>/setting/backup/parquet/report/list</t>
+          <t>/setting/backup/parquet/report/download-all</t>
         </is>
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>list_report_files</t>
+          <t>download_all_reports</t>
         </is>
       </c>
       <c r="F151" s="16" t="inlineStr">
@@ -19553,22 +19597,22 @@
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>/setting/backup/start</t>
+          <t>/setting/backup/parquet/report/list</t>
         </is>
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>start_backup</t>
+          <t>list_report_files</t>
         </is>
       </c>
       <c r="F152" s="16" t="inlineStr">
         <is>
-          <t>CommandPanel.vue</t>
+          <t>ServicePanel_New.vue</t>
         </is>
       </c>
     </row>
@@ -19583,17 +19627,17 @@
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>/setting/backup/status/{task_id}</t>
+          <t>/setting/backup/start</t>
         </is>
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>get_backup_status</t>
+          <t>start_backup</t>
         </is>
       </c>
       <c r="F153" s="16" t="inlineStr">
@@ -19618,17 +19662,17 @@
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>/setting/checkFRP</t>
+          <t>/setting/backup/status/{task_id}</t>
         </is>
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>check_frp</t>
+          <t>get_backup_status</t>
         </is>
       </c>
       <c r="F154" s="16" t="inlineStr">
         <is>
-          <t>SettingNew.vue</t>
+          <t>CommandPanel.vue</t>
         </is>
       </c>
     </row>
@@ -19648,17 +19692,17 @@
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t>/setting/recreateBuckets</t>
+          <t>/setting/checkFRP</t>
         </is>
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>recreate_buckets</t>
+          <t>check_frp</t>
         </is>
       </c>
       <c r="F155" s="16" t="inlineStr">
         <is>
-          <t>(프론트엔드 미사용)</t>
+          <t>SettingNew.vue</t>
         </is>
       </c>
     </row>
@@ -19673,17 +19717,17 @@
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>/setting/recreateDownsamplingTasks</t>
+          <t>/setting/recreateBuckets</t>
         </is>
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>api_recreate_downsampling_tasks</t>
+          <t>recreate_buckets</t>
         </is>
       </c>
       <c r="F156" s="16" t="inlineStr">
@@ -19703,17 +19747,17 @@
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="D157" s="3" t="inlineStr">
         <is>
-          <t>/setting/restoreInflux/{org_id}/{token}</t>
+          <t>/setting/recreateDownsamplingTasks</t>
         </is>
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>restore_influxToken</t>
+          <t>api_recreate_downsampling_tasks</t>
         </is>
       </c>
       <c r="F157" s="16" t="inlineStr">
@@ -19733,59 +19777,59 @@
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D158" s="3" t="inlineStr">
+        <is>
+          <t>/setting/restoreInflux/{org_id}/{token}</t>
+        </is>
+      </c>
+      <c r="E158" s="3" t="inlineStr">
+        <is>
+          <t>restore_influxToken</t>
+        </is>
+      </c>
+      <c r="F158" s="16" t="inlineStr">
+        <is>
+          <t>(프론트엔드 미사용)</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="3" t="n">
+        <v>154</v>
+      </c>
+      <c r="B159" s="6" t="inlineStr">
+        <is>
+          <t>/setting</t>
+        </is>
+      </c>
+      <c r="C159" s="4" t="inlineStr">
+        <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="D158" s="3" t="inlineStr">
+      <c r="D159" s="3" t="inlineStr">
         <is>
           <t>/setting/setSystemTime</t>
         </is>
       </c>
-      <c r="E158" s="3" t="inlineStr">
+      <c r="E159" s="3" t="inlineStr">
         <is>
           <t>setup_system_time</t>
         </is>
       </c>
-      <c r="F158" s="16" t="inlineStr">
+      <c r="F159" s="16" t="inlineStr">
         <is>
           <t>DropdownClock.vue</t>
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="15" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="15" t="inlineStr">
         <is>
           <t>/config (configRouter - routes/config.py)</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="3" t="n">
-        <v>154</v>
-      </c>
-      <c r="B160" s="8" t="inlineStr">
-        <is>
-          <t>/config</t>
-        </is>
-      </c>
-      <c r="C160" s="7" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D160" s="3" t="inlineStr">
-        <is>
-          <t>/config/upload</t>
-        </is>
-      </c>
-      <c r="E160" s="3" t="inlineStr">
-        <is>
-          <t>upload_file</t>
-        </is>
-      </c>
-      <c r="F160" s="3" t="inlineStr">
-        <is>
-          <t>CaliSideBar2.vue</t>
         </is>
       </c>
     </row>
@@ -19798,19 +19842,19 @@
           <t>/config</t>
         </is>
       </c>
-      <c r="C161" s="4" t="inlineStr">
-        <is>
-          <t>GET</t>
+      <c r="C161" s="7" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
         <is>
-          <t>/config/checkSetup</t>
+          <t>/config/upload</t>
         </is>
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>check_setup</t>
+          <t>upload_file</t>
         </is>
       </c>
       <c r="F161" s="3" t="inlineStr">
@@ -19835,17 +19879,17 @@
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
-          <t>/config/calibrateNow</t>
+          <t>/config/checkSetup</t>
         </is>
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>cali_mount</t>
+          <t>check_setup</t>
         </is>
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
-          <t>Calibrate2.vue</t>
+          <t>CaliSideBar2.vue</t>
         </is>
       </c>
     </row>
@@ -19865,17 +19909,17 @@
       </c>
       <c r="D163" s="3" t="inlineStr">
         <is>
-          <t>/config/calibrate/applySetup</t>
+          <t>/config/calibrateNow</t>
         </is>
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>cali_setup</t>
+          <t>cali_mount</t>
         </is>
       </c>
       <c r="F163" s="3" t="inlineStr">
         <is>
-          <t>CaliSideBar2.vue</t>
+          <t>Calibrate2.vue</t>
         </is>
       </c>
     </row>
@@ -19888,19 +19932,19 @@
           <t>/config</t>
         </is>
       </c>
-      <c r="C164" s="7" t="inlineStr">
-        <is>
-          <t>POST</t>
+      <c r="C164" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
-          <t>/config/calibrate/saveRef</t>
+          <t>/config/calibrate/applySetup</t>
         </is>
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
-          <t>set_saveref</t>
+          <t>cali_setup</t>
         </is>
       </c>
       <c r="F164" s="3" t="inlineStr">
@@ -19918,19 +19962,19 @@
           <t>/config</t>
         </is>
       </c>
-      <c r="C165" s="4" t="inlineStr">
-        <is>
-          <t>GET</t>
+      <c r="C165" s="7" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D165" s="3" t="inlineStr">
         <is>
-          <t>/config/calibrate/start</t>
+          <t>/config/calibrate/saveRef</t>
         </is>
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>cali_start</t>
+          <t>set_saveref</t>
         </is>
       </c>
       <c r="F165" s="3" t="inlineStr">
@@ -19955,12 +19999,12 @@
       </c>
       <c r="D166" s="3" t="inlineStr">
         <is>
-          <t>/config/calibrate/end</t>
+          <t>/config/calibrate/start</t>
         </is>
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
-          <t>cali_end</t>
+          <t>cali_start</t>
         </is>
       </c>
       <c r="F166" s="3" t="inlineStr">
@@ -19978,19 +20022,19 @@
           <t>/config</t>
         </is>
       </c>
-      <c r="C167" s="7" t="inlineStr">
-        <is>
-          <t>POST</t>
+      <c r="C167" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="D167" s="3" t="inlineStr">
         <is>
-          <t>/config/calibrate/cmd</t>
+          <t>/config/calibrate/end</t>
         </is>
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>set_cmd</t>
+          <t>cali_end</t>
         </is>
       </c>
       <c r="F167" s="3" t="inlineStr">
@@ -20008,19 +20052,19 @@
           <t>/config</t>
         </is>
       </c>
-      <c r="C168" s="4" t="inlineStr">
-        <is>
-          <t>GET</t>
+      <c r="C168" s="7" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D168" s="3" t="inlineStr">
         <is>
-          <t>/config/calibrate/gettime</t>
+          <t>/config/calibrate/cmd</t>
         </is>
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
-          <t>get_device_time</t>
+          <t>set_cmd</t>
         </is>
       </c>
       <c r="F168" s="3" t="inlineStr">
@@ -20038,24 +20082,24 @@
           <t>/config</t>
         </is>
       </c>
-      <c r="C169" s="7" t="inlineStr">
-        <is>
-          <t>POST</t>
+      <c r="C169" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="D169" s="3" t="inlineStr">
         <is>
-          <t>/config/calibrate/setSystemTime</t>
+          <t>/config/calibrate/gettime</t>
         </is>
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>set_system_time</t>
+          <t>get_device_time</t>
         </is>
       </c>
       <c r="F169" s="3" t="inlineStr">
         <is>
-          <t>CaliSideBar2, DropdownClock</t>
+          <t>CaliSideBar2.vue</t>
         </is>
       </c>
     </row>
@@ -20075,17 +20119,17 @@
       </c>
       <c r="D170" s="3" t="inlineStr">
         <is>
-          <t>/config/checktime</t>
+          <t>/config/calibrate/setSystemTime</t>
         </is>
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
-          <t>check_device_time</t>
+          <t>set_system_time</t>
         </is>
       </c>
       <c r="F170" s="3" t="inlineStr">
         <is>
-          <t>Header.vue</t>
+          <t>CaliSideBar2, DropdownClock</t>
         </is>
       </c>
     </row>
@@ -20105,17 +20149,17 @@
       </c>
       <c r="D171" s="3" t="inlineStr">
         <is>
-          <t>/config/savePost/{mode}/{idx}</t>
+          <t>/config/checktime</t>
         </is>
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
-          <t>save_maintanence</t>
+          <t>check_device_time</t>
         </is>
       </c>
       <c r="F171" s="3" t="inlineStr">
         <is>
-          <t>MaintenancePanel.vue</t>
+          <t>Header.vue</t>
         </is>
       </c>
     </row>
@@ -20128,19 +20172,19 @@
           <t>/config</t>
         </is>
       </c>
-      <c r="C172" s="4" t="inlineStr">
-        <is>
-          <t>GET</t>
+      <c r="C172" s="7" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
-          <t>/config/getPost</t>
+          <t>/config/savePost/{mode}/{idx}</t>
         </is>
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>get_post</t>
+          <t>save_maintanence</t>
         </is>
       </c>
       <c r="F172" s="3" t="inlineStr">
@@ -20165,12 +20209,12 @@
       </c>
       <c r="D173" s="3" t="inlineStr">
         <is>
-          <t>/config/getLastPost</t>
+          <t>/config/getPost</t>
         </is>
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>get_last</t>
+          <t>get_post</t>
         </is>
       </c>
       <c r="F173" s="3" t="inlineStr">
@@ -20195,12 +20239,12 @@
       </c>
       <c r="D174" s="3" t="inlineStr">
         <is>
-          <t>/config/deletePost/{idx}</t>
+          <t>/config/getLastPost</t>
         </is>
       </c>
       <c r="E174" s="3" t="inlineStr">
         <is>
-          <t>delete_post</t>
+          <t>get_last</t>
         </is>
       </c>
       <c r="F174" s="3" t="inlineStr">
@@ -20225,17 +20269,17 @@
       </c>
       <c r="D175" s="3" t="inlineStr">
         <is>
-          <t>/config/getLog</t>
+          <t>/config/deletePost/{idx}</t>
         </is>
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
-          <t>get_log</t>
+          <t>delete_post</t>
         </is>
       </c>
       <c r="F175" s="3" t="inlineStr">
         <is>
-          <t>LogPanel.vue</t>
+          <t>MaintenancePanel.vue</t>
         </is>
       </c>
     </row>
@@ -20255,17 +20299,17 @@
       </c>
       <c r="D176" s="3" t="inlineStr">
         <is>
-          <t>/config/applog/recent/{item}</t>
+          <t>/config/getLog</t>
         </is>
       </c>
       <c r="E176" s="3" t="inlineStr">
         <is>
-          <t>get_recent_logs</t>
+          <t>get_log</t>
         </is>
       </c>
       <c r="F176" s="3" t="inlineStr">
         <is>
-          <t>appLogModal.vue</t>
+          <t>LogPanel.vue</t>
         </is>
       </c>
     </row>
@@ -20285,17 +20329,17 @@
       </c>
       <c r="D177" s="3" t="inlineStr">
         <is>
-          <t>/config/calibrate/getUnbal</t>
+          <t>/config/applog/recent/{item}</t>
         </is>
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
-          <t>getUnbal</t>
-        </is>
-      </c>
-      <c r="F177" s="16" t="inlineStr">
-        <is>
-          <t>(프론트엔드 미사용)</t>
+          <t>get_recent_logs</t>
+        </is>
+      </c>
+      <c r="F177" s="3" t="inlineStr">
+        <is>
+          <t>appLogModal.vue</t>
         </is>
       </c>
     </row>
@@ -20303,24 +20347,24 @@
       <c r="A178" s="3" t="n">
         <v>172</v>
       </c>
-      <c r="B178" s="6" t="inlineStr">
+      <c r="B178" s="8" t="inlineStr">
         <is>
           <t>/config</t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D178" s="3" t="inlineStr">
         <is>
-          <t>/config/backup/restore/influxdb</t>
+          <t>/config/calibrate/getUnbal</t>
         </is>
       </c>
       <c r="E178" s="3" t="inlineStr">
         <is>
-          <t>restore_influxdb</t>
+          <t>getUnbal</t>
         </is>
       </c>
       <c r="F178" s="16" t="inlineStr">
@@ -20345,12 +20389,12 @@
       </c>
       <c r="D179" s="3" t="inlineStr">
         <is>
-          <t>/config/backup/restore/smartsystems</t>
+          <t>/config/backup/restore/influxdb</t>
         </is>
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
-          <t>restore_smartsystems</t>
+          <t>restore_influxdb</t>
         </is>
       </c>
       <c r="F179" s="16" t="inlineStr">
@@ -20370,22 +20414,22 @@
       </c>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D180" s="3" t="inlineStr">
         <is>
-          <t>/config/deleteLog</t>
+          <t>/config/backup/restore/smartsystems</t>
         </is>
       </c>
       <c r="E180" s="3" t="inlineStr">
         <is>
-          <t>delete_all_logs</t>
+          <t>restore_smartsystems</t>
         </is>
       </c>
       <c r="F180" s="16" t="inlineStr">
         <is>
-          <t>LogPanel.vue</t>
+          <t>(프론트엔드 미사용)</t>
         </is>
       </c>
     </row>
@@ -20400,22 +20444,22 @@
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="D181" s="3" t="inlineStr">
         <is>
-          <t>/config/getReleaseNote/{lang}/{version}</t>
+          <t>/config/deleteLog</t>
         </is>
       </c>
       <c r="E181" s="3" t="inlineStr">
         <is>
-          <t>get_release_note</t>
+          <t>delete_all_logs</t>
         </is>
       </c>
       <c r="F181" s="16" t="inlineStr">
         <is>
-          <t>MaintenancePanel.vue</t>
+          <t>LogPanel.vue</t>
         </is>
       </c>
     </row>
@@ -20435,12 +20479,12 @@
       </c>
       <c r="D182" s="3" t="inlineStr">
         <is>
-          <t>/config/getReleaseNotes</t>
+          <t>/config/getReleaseNote/{lang}/{version}</t>
         </is>
       </c>
       <c r="E182" s="3" t="inlineStr">
         <is>
-          <t>get_release_notes</t>
+          <t>get_release_note</t>
         </is>
       </c>
       <c r="F182" s="16" t="inlineStr">
@@ -20465,17 +20509,17 @@
       </c>
       <c r="D183" s="3" t="inlineStr">
         <is>
-          <t>/config/getTrain/download/{channel}/{start}</t>
+          <t>/config/getReleaseNotes</t>
         </is>
       </c>
       <c r="E183" s="3" t="inlineStr">
         <is>
-          <t>download_train</t>
+          <t>get_release_notes</t>
         </is>
       </c>
       <c r="F183" s="16" t="inlineStr">
         <is>
-          <t>ServicePanel_New.vue</t>
+          <t>MaintenancePanel.vue</t>
         </is>
       </c>
     </row>
@@ -20495,12 +20539,12 @@
       </c>
       <c r="D184" s="3" t="inlineStr">
         <is>
-          <t>/config/getTrain/range/{channel}</t>
+          <t>/config/getTrain/download/{channel}/{start}</t>
         </is>
       </c>
       <c r="E184" s="3" t="inlineStr">
         <is>
-          <t>get_train_range</t>
+          <t>download_train</t>
         </is>
       </c>
       <c r="F184" s="16" t="inlineStr">
@@ -20520,17 +20564,17 @@
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D185" s="3" t="inlineStr">
         <is>
-          <t>/config/getTrain/start/{channel}/{start}</t>
+          <t>/config/getTrain/range/{channel}</t>
         </is>
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>start_train_collect</t>
+          <t>get_train_range</t>
         </is>
       </c>
       <c r="F185" s="16" t="inlineStr">
@@ -20550,59 +20594,59 @@
       </c>
       <c r="C186" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D186" s="3" t="inlineStr">
         <is>
+          <t>/config/getTrain/start/{channel}/{start}</t>
+        </is>
+      </c>
+      <c r="E186" s="3" t="inlineStr">
+        <is>
+          <t>start_train_collect</t>
+        </is>
+      </c>
+      <c r="F186" s="16" t="inlineStr">
+        <is>
+          <t>ServicePanel_New.vue</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="3" t="n">
+        <v>181</v>
+      </c>
+      <c r="B187" s="6" t="inlineStr">
+        <is>
+          <t>/config</t>
+        </is>
+      </c>
+      <c r="C187" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D187" s="3" t="inlineStr">
+        <is>
           <t>/config/getTrain/status/{task_id}</t>
         </is>
       </c>
-      <c r="E186" s="3" t="inlineStr">
+      <c r="E187" s="3" t="inlineStr">
         <is>
           <t>get_train_status</t>
         </is>
       </c>
-      <c r="F186" s="16" t="inlineStr">
+      <c r="F187" s="16" t="inlineStr">
         <is>
           <t>ServicePanel_New.vue</t>
         </is>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" s="15" t="inlineStr">
+    <row r="188">
+      <c r="A188" s="15" t="inlineStr">
         <is>
           <t>/report (reportRouter - routes/report.py)</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" s="3" t="n">
-        <v>181</v>
-      </c>
-      <c r="B188" s="12" t="inlineStr">
-        <is>
-          <t>/report</t>
-        </is>
-      </c>
-      <c r="C188" s="7" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D188" s="3" t="inlineStr">
-        <is>
-          <t>/report/generate</t>
-        </is>
-      </c>
-      <c r="E188" s="3" t="inlineStr">
-        <is>
-          <t>set_report</t>
-        </is>
-      </c>
-      <c r="F188" s="3" t="inlineStr">
-        <is>
-          <t>reportDict.js</t>
         </is>
       </c>
     </row>
@@ -20615,24 +20659,24 @@
           <t>/report</t>
         </is>
       </c>
-      <c r="C189" s="4" t="inlineStr">
-        <is>
-          <t>GET</t>
+      <c r="C189" s="7" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D189" s="3" t="inlineStr">
         <is>
-          <t>/report/lastReportData/{mode}/{asset_name}</t>
+          <t>/report/generate</t>
         </is>
       </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
-          <t>get_last_diagnosis</t>
+          <t>set_report</t>
         </is>
       </c>
       <c r="F189" s="3" t="inlineStr">
         <is>
-          <t>ReportNew, Report_Diagnosis_accordion2, Report_Diagnosis_HBarTab</t>
+          <t>reportDict.js</t>
         </is>
       </c>
     </row>
@@ -20652,12 +20696,12 @@
       </c>
       <c r="D190" s="3" t="inlineStr">
         <is>
-          <t>/report/reportTimes/{date}/{asset}/{mode}</t>
+          <t>/report/lastReportData/{mode}/{asset_name}</t>
         </is>
       </c>
       <c r="E190" s="3" t="inlineStr">
         <is>
-          <t>get_report_times</t>
+          <t>get_last_diagnosis</t>
         </is>
       </c>
       <c r="F190" s="3" t="inlineStr">
@@ -20682,12 +20726,12 @@
       </c>
       <c r="D191" s="3" t="inlineStr">
         <is>
-          <t>/report/reportDataByTime/{mode}/{asset}/{ts}</t>
+          <t>/report/reportTimes/{date}/{asset}/{mode}</t>
         </is>
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
-          <t>get_report_data_by_time</t>
+          <t>get_report_times</t>
         </is>
       </c>
       <c r="F191" s="3" t="inlineStr">
@@ -20712,17 +20756,17 @@
       </c>
       <c r="D192" s="3" t="inlineStr">
         <is>
-          <t>/report/status_trend/{mode}/{asset}/{item}</t>
+          <t>/report/reportDataByTime/{mode}/{asset}/{ts}</t>
         </is>
       </c>
       <c r="E192" s="3" t="inlineStr">
         <is>
-          <t>get_item_trend</t>
+          <t>get_report_data_by_time</t>
         </is>
       </c>
       <c r="F192" s="3" t="inlineStr">
         <is>
-          <t>Report_Diagnosis_New.vue</t>
+          <t>ReportNew, Report_Diagnosis_accordion2, Report_Diagnosis_HBarTab</t>
         </is>
       </c>
     </row>
@@ -20742,17 +20786,17 @@
       </c>
       <c r="D193" s="3" t="inlineStr">
         <is>
-          <t>/report/downloadDiagnosisReport/{mode}/{asset}/{ch}/{ts:path}</t>
+          <t>/report/status_trend/{mode}/{asset}/{item}</t>
         </is>
       </c>
       <c r="E193" s="3" t="inlineStr">
         <is>
-          <t>download_diagnosis_report</t>
+          <t>get_item_trend</t>
         </is>
       </c>
       <c r="F193" s="3" t="inlineStr">
         <is>
-          <t>Report_Diagnosis_HBarTab.vue</t>
+          <t>Report_Diagnosis_New.vue</t>
         </is>
       </c>
     </row>
@@ -20772,17 +20816,17 @@
       </c>
       <c r="D194" s="3" t="inlineStr">
         <is>
-          <t>/report/week/{channel}/{filename}</t>
+          <t>/report/downloadDiagnosisReport/{mode}/{asset}/{ch}/{ts:path}</t>
         </is>
       </c>
       <c r="E194" s="3" t="inlineStr">
         <is>
-          <t>get_weekly_report</t>
+          <t>download_diagnosis_report</t>
         </is>
       </c>
       <c r="F194" s="3" t="inlineStr">
         <is>
-          <t>ReportNew.vue</t>
+          <t>Report_Diagnosis_HBarTab.vue</t>
         </is>
       </c>
     </row>
@@ -20802,12 +20846,12 @@
       </c>
       <c r="D195" s="3" t="inlineStr">
         <is>
-          <t>/report/list/{channel}</t>
+          <t>/report/week/{channel}/{filename}</t>
         </is>
       </c>
       <c r="E195" s="3" t="inlineStr">
         <is>
-          <t>get_filelist</t>
+          <t>get_weekly_report</t>
         </is>
       </c>
       <c r="F195" s="3" t="inlineStr">
@@ -20832,12 +20876,12 @@
       </c>
       <c r="D196" s="3" t="inlineStr">
         <is>
-          <t>/report/getReportDiagnosis/{mode}/{asset}/{ch}/{date}</t>
+          <t>/report/list/{channel}</t>
         </is>
       </c>
       <c r="E196" s="3" t="inlineStr">
         <is>
-          <t>get_report_diagnosis_data</t>
+          <t>get_filelist</t>
         </is>
       </c>
       <c r="F196" s="3" t="inlineStr">
@@ -20862,12 +20906,12 @@
       </c>
       <c r="D197" s="3" t="inlineStr">
         <is>
-          <t>/report/downloadWeeklyReport/{channel}/{date}</t>
+          <t>/report/getReportDiagnosis/{mode}/{asset}/{ch}/{date}</t>
         </is>
       </c>
       <c r="E197" s="3" t="inlineStr">
         <is>
-          <t>download_weekly_report</t>
+          <t>get_report_diagnosis_data</t>
         </is>
       </c>
       <c r="F197" s="3" t="inlineStr">
@@ -20892,17 +20936,17 @@
       </c>
       <c r="D198" s="3" t="inlineStr">
         <is>
-          <t>/report/weeklyReportData/{channel}/{date}</t>
+          <t>/report/downloadWeeklyReport/{channel}/{date}</t>
         </is>
       </c>
       <c r="E198" s="3" t="inlineStr">
         <is>
-          <t>get_weekly_report_data</t>
-        </is>
-      </c>
-      <c r="F198" s="16" t="inlineStr">
-        <is>
-          <t>(프론트엔드 미사용)</t>
+          <t>download_weekly_report</t>
+        </is>
+      </c>
+      <c r="F198" s="3" t="inlineStr">
+        <is>
+          <t>ReportNew.vue</t>
         </is>
       </c>
     </row>
@@ -20910,7 +20954,7 @@
       <c r="A199" s="3" t="n">
         <v>192</v>
       </c>
-      <c r="B199" s="6" t="inlineStr">
+      <c r="B199" s="12" t="inlineStr">
         <is>
           <t>/report</t>
         </is>
@@ -20922,17 +20966,17 @@
       </c>
       <c r="D199" s="3" t="inlineStr">
         <is>
-          <t>/report/weeklyReport/download/{task_id}</t>
+          <t>/report/weeklyReportData/{channel}/{date}</t>
         </is>
       </c>
       <c r="E199" s="3" t="inlineStr">
         <is>
-          <t>download_weekly_report_file</t>
+          <t>get_weekly_report_data</t>
         </is>
       </c>
       <c r="F199" s="16" t="inlineStr">
         <is>
-          <t>ReportNew3.vue</t>
+          <t>(프론트엔드 미사용)</t>
         </is>
       </c>
     </row>
@@ -20952,12 +20996,12 @@
       </c>
       <c r="D200" s="3" t="inlineStr">
         <is>
-          <t>/report/weeklyReport/start/{channel}/{date}</t>
+          <t>/report/weeklyReport/download/{task_id}</t>
         </is>
       </c>
       <c r="E200" s="3" t="inlineStr">
         <is>
-          <t>start_weekly_report</t>
+          <t>download_weekly_report_file</t>
         </is>
       </c>
       <c r="F200" s="16" t="inlineStr">
@@ -20982,54 +21026,54 @@
       </c>
       <c r="D201" s="3" t="inlineStr">
         <is>
+          <t>/report/weeklyReport/start/{channel}/{date}</t>
+        </is>
+      </c>
+      <c r="E201" s="3" t="inlineStr">
+        <is>
+          <t>start_weekly_report</t>
+        </is>
+      </c>
+      <c r="F201" s="16" t="inlineStr">
+        <is>
+          <t>ReportNew3.vue</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="B202" s="6" t="inlineStr">
+        <is>
+          <t>/report</t>
+        </is>
+      </c>
+      <c r="C202" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D202" s="3" t="inlineStr">
+        <is>
           <t>/report/weeklyReport/status/{task_id}</t>
         </is>
       </c>
-      <c r="E201" s="3" t="inlineStr">
+      <c r="E202" s="3" t="inlineStr">
         <is>
           <t>get_weekly_report_status</t>
         </is>
       </c>
-      <c r="F201" s="16" t="inlineStr">
+      <c r="F202" s="16" t="inlineStr">
         <is>
           <t>ReportNew3.vue</t>
         </is>
       </c>
     </row>
-    <row r="202">
-      <c r="A202" s="15" t="inlineStr">
+    <row r="203">
+      <c r="A203" s="15" t="inlineStr">
         <is>
           <t>/master (masterRouter - routes/master.py)</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" s="3" t="n">
-        <v>195</v>
-      </c>
-      <c r="B203" s="10" t="inlineStr">
-        <is>
-          <t>/master</t>
-        </is>
-      </c>
-      <c r="C203" s="4" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="D203" s="3" t="inlineStr">
-        <is>
-          <t>/master/getSetup/{ip}</t>
-        </is>
-      </c>
-      <c r="E203" s="3" t="inlineStr">
-        <is>
-          <t>getSetup</t>
-        </is>
-      </c>
-      <c r="F203" s="16" t="inlineStr">
-        <is>
-          <t>(프론트엔드 미사용)</t>
         </is>
       </c>
     </row>
@@ -21042,24 +21086,24 @@
           <t>/master</t>
         </is>
       </c>
-      <c r="C204" s="7" t="inlineStr">
-        <is>
-          <t>POST</t>
+      <c r="C204" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="D204" s="3" t="inlineStr">
         <is>
-          <t>/master/saveDevice</t>
+          <t>/master/getSetup/{ip}</t>
         </is>
       </c>
       <c r="E204" s="3" t="inlineStr">
         <is>
-          <t>save_device</t>
-        </is>
-      </c>
-      <c r="F204" s="3" t="inlineStr">
-        <is>
-          <t>MasterDashboard.vue</t>
+          <t>getSetup</t>
+        </is>
+      </c>
+      <c r="F204" s="16" t="inlineStr">
+        <is>
+          <t>(프론트엔드 미사용)</t>
         </is>
       </c>
     </row>
@@ -21072,19 +21116,19 @@
           <t>/master</t>
         </is>
       </c>
-      <c r="C205" s="4" t="inlineStr">
-        <is>
-          <t>GET</t>
+      <c r="C205" s="7" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D205" s="3" t="inlineStr">
         <is>
-          <t>/master/deleteDevice/{id}</t>
+          <t>/master/saveDevice</t>
         </is>
       </c>
       <c r="E205" s="3" t="inlineStr">
         <is>
-          <t>delete_device</t>
+          <t>save_device</t>
         </is>
       </c>
       <c r="F205" s="3" t="inlineStr">
@@ -21109,17 +21153,17 @@
       </c>
       <c r="D206" s="3" t="inlineStr">
         <is>
-          <t>/master/getStatus/{ip}/{asset}</t>
+          <t>/master/deleteDevice/{id}</t>
         </is>
       </c>
       <c r="E206" s="3" t="inlineStr">
         <is>
-          <t>getStatus</t>
-        </is>
-      </c>
-      <c r="F206" s="16" t="inlineStr">
-        <is>
-          <t>(프론트엔드 미사용)</t>
+          <t>delete_device</t>
+        </is>
+      </c>
+      <c r="F206" s="3" t="inlineStr">
+        <is>
+          <t>MasterDashboard.vue</t>
         </is>
       </c>
     </row>
@@ -21139,54 +21183,54 @@
       </c>
       <c r="D207" s="3" t="inlineStr">
         <is>
+          <t>/master/getStatus/{ip}/{asset}</t>
+        </is>
+      </c>
+      <c r="E207" s="3" t="inlineStr">
+        <is>
+          <t>getStatus</t>
+        </is>
+      </c>
+      <c r="F207" s="16" t="inlineStr">
+        <is>
+          <t>(프론트엔드 미사용)</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="B208" s="10" t="inlineStr">
+        <is>
+          <t>/master</t>
+        </is>
+      </c>
+      <c r="C208" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D208" s="3" t="inlineStr">
+        <is>
           <t>/master/getDeviceInfo</t>
         </is>
       </c>
-      <c r="E207" s="3" t="inlineStr">
+      <c r="E208" s="3" t="inlineStr">
         <is>
           <t>getDeviceInfo</t>
         </is>
       </c>
-      <c r="F207" s="3" t="inlineStr">
+      <c r="F208" s="3" t="inlineStr">
         <is>
           <t>MasterDashboard.vue</t>
         </is>
       </c>
     </row>
-    <row r="208">
-      <c r="A208" s="15" t="inlineStr">
+    <row r="209">
+      <c r="A209" s="15" t="inlineStr">
         <is>
           <t>/demand (demandRouter - routes/demand.py)</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" s="3" t="n">
-        <v>200</v>
-      </c>
-      <c r="B209" s="6" t="inlineStr">
-        <is>
-          <t>/demand</t>
-        </is>
-      </c>
-      <c r="C209" s="4" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="D209" s="3" t="inlineStr">
-        <is>
-          <t>/demand/heatmap/{channel}</t>
-        </is>
-      </c>
-      <c r="E209" s="3" t="inlineStr">
-        <is>
-          <t>get_demand_heatmap</t>
-        </is>
-      </c>
-      <c r="F209" s="16" t="inlineStr">
-        <is>
-          <t>reportDict.js</t>
         </is>
       </c>
     </row>
@@ -21206,12 +21250,12 @@
       </c>
       <c r="D210" s="3" t="inlineStr">
         <is>
-          <t>/demand/load-factor-monthly/{channel}</t>
+          <t>/demand/heatmap/{channel}</t>
         </is>
       </c>
       <c r="E210" s="3" t="inlineStr">
         <is>
-          <t>get_demand_load_factor_monthly</t>
+          <t>get_demand_heatmap</t>
         </is>
       </c>
       <c r="F210" s="16" t="inlineStr">
@@ -21236,12 +21280,12 @@
       </c>
       <c r="D211" s="3" t="inlineStr">
         <is>
-          <t>/demand/summary/{channel}</t>
+          <t>/demand/load-factor-monthly/{channel}</t>
         </is>
       </c>
       <c r="E211" s="3" t="inlineStr">
         <is>
-          <t>get_demand_summary</t>
+          <t>get_demand_load_factor_monthly</t>
         </is>
       </c>
       <c r="F211" s="16" t="inlineStr">
@@ -21266,15 +21310,45 @@
       </c>
       <c r="D212" s="3" t="inlineStr">
         <is>
+          <t>/demand/summary/{channel}</t>
+        </is>
+      </c>
+      <c r="E212" s="3" t="inlineStr">
+        <is>
+          <t>get_demand_summary</t>
+        </is>
+      </c>
+      <c r="F212" s="16" t="inlineStr">
+        <is>
+          <t>reportDict.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="3" t="n">
+        <v>204</v>
+      </c>
+      <c r="B213" s="6" t="inlineStr">
+        <is>
+          <t>/demand</t>
+        </is>
+      </c>
+      <c r="C213" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D213" s="3" t="inlineStr">
+        <is>
           <t>/demand/trend/{channel}</t>
         </is>
       </c>
-      <c r="E212" s="3" t="inlineStr">
+      <c r="E213" s="3" t="inlineStr">
         <is>
           <t>get_demand_trend</t>
         </is>
       </c>
-      <c r="F212" s="16" t="inlineStr">
+      <c r="F213" s="16" t="inlineStr">
         <is>
           <t>reportDict.js</t>
         </is>
@@ -21725,7 +21799,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
         <is>
@@ -21771,13 +21844,13 @@
         </is>
       </c>
       <c r="B5" s="19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C5" s="19" t="n">
         <v>55</v>
       </c>
       <c r="D5" s="19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -21867,16 +21940,15 @@
         </is>
       </c>
       <c r="B11" s="25" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C11" s="25" t="n">
         <v>161</v>
       </c>
       <c r="D11" s="25" t="n">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="12"/>
+        <v>40</v>
+      </c>
+    </row>
     <row r="13">
       <c r="A13" s="26" t="inlineStr">
         <is>
@@ -22012,7 +22084,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>~203개 (코드 대조 2026-06-15)</t>
+          <t>~204개 (코드 대조 2026-06-15, +getHarmonicsTrend)</t>
         </is>
       </c>
     </row>
@@ -22068,7 +22140,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E197"/>
+  <dimension ref="A1:E198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -26036,17 +26108,17 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>(공통),/</t>
+          <t>(공통),/trend</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>partials/modeview/dashboard2/DualMeasCard_Diagnosis_v2.vue</t>
+          <t>partials/inners/trend/HarmonicsTab.vue</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>partials/dashboard2/DualMeasCard_Diagnosis_v2.vue</t>
+          <t>partials/trend/HarmonicsTab.vue</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -26066,12 +26138,12 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>partials/modeview/dashboard2/DualMeasCard_Meter_v2.vue</t>
+          <t>partials/modeview/dashboard2/DualMeasCard_Diagnosis_v2.vue</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>partials/dashboard2/DualMeasCard_Meter_v2.vue</t>
+          <t>partials/dashboard2/DualMeasCard_Diagnosis_v2.vue</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -26091,12 +26163,12 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>partials/modeview/dashboard2/DualMeasCard_THD_v2.vue</t>
+          <t>partials/modeview/dashboard2/DualMeasCard_Meter_v2.vue</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>partials/dashboard2/DualMeasCard_THD_v2.vue</t>
+          <t>partials/dashboard2/DualMeasCard_Meter_v2.vue</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -26116,12 +26188,12 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>partials/modeview/dashboard2/MeasCard_Energy.vue</t>
+          <t>partials/modeview/dashboard2/DualMeasCard_THD_v2.vue</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>partials/dashboard2/MeasCard_Energy.vue</t>
+          <t>partials/dashboard2/DualMeasCard_THD_v2.vue</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -26141,12 +26213,12 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>partials/modeview/dashboard2/MeasCard_EventLog.vue</t>
+          <t>partials/modeview/dashboard2/MeasCard_Energy.vue</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>partials/dashboard2/MeasCard_EventLog.vue</t>
+          <t>partials/dashboard2/MeasCard_Energy.vue</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -26166,12 +26238,12 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>partials/modeview/dashboard2/MeasCard_PQ.vue</t>
+          <t>partials/modeview/dashboard2/MeasCard_EventLog.vue</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>partials/dashboard2/MeasCard_PQ.vue</t>
+          <t>partials/dashboard2/MeasCard_EventLog.vue</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -26191,12 +26263,12 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>partials/modeview/dashboard2/MeasCard_PowerFactor.vue</t>
+          <t>partials/modeview/dashboard2/MeasCard_PQ.vue</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>partials/dashboard2/MeasCard_PowerFactor.vue</t>
+          <t>partials/dashboard2/MeasCard_PQ.vue</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -26216,12 +26288,12 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>partials/modeview/dashboard2/MeasCard_Voltage.vue</t>
+          <t>partials/modeview/dashboard2/MeasCard_PowerFactor.vue</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>partials/dashboard2/MeasCard_Voltage.vue</t>
+          <t>partials/dashboard2/MeasCard_PowerFactor.vue</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -26241,12 +26313,12 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>partials/modeview/dashboard2/SingleMeasCard_Diagnosis.vue</t>
+          <t>partials/modeview/dashboard2/MeasCard_Voltage.vue</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>partials/dashboard2/SingleMeasCard_Diagnosis.vue</t>
+          <t>partials/dashboard2/MeasCard_Voltage.vue</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -26266,12 +26338,12 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>partials/modeview/dashboard2/SingleMeasCard_Energy.vue</t>
+          <t>partials/modeview/dashboard2/SingleMeasCard_Diagnosis.vue</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>partials/dashboard2/SingleMeasCard_Energy.vue</t>
+          <t>partials/dashboard2/SingleMeasCard_Diagnosis.vue</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -26291,12 +26363,12 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>partials/modeview/dashboard2/SingleMeasCard_Equip.vue</t>
+          <t>partials/modeview/dashboard2/SingleMeasCard_Energy.vue</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>partials/dashboard2/SingleMeasCard_Equip.vue</t>
+          <t>partials/dashboard2/SingleMeasCard_Energy.vue</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -26316,12 +26388,12 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>partials/modeview/dashboard2/SingleMeasCard_Meter.vue</t>
+          <t>partials/modeview/dashboard2/SingleMeasCard_Equip.vue</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>partials/dashboard2/SingleMeasCard_Meter.vue</t>
+          <t>partials/dashboard2/SingleMeasCard_Equip.vue</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -26341,12 +26413,12 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>partials/modeview/dashboard2/SingleMeasCard_PQ.vue</t>
+          <t>partials/modeview/dashboard2/SingleMeasCard_Meter.vue</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>partials/dashboard2/SingleMeasCard_PQ.vue</t>
+          <t>partials/dashboard2/SingleMeasCard_Meter.vue</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -26366,12 +26438,12 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>partials/modeview/dashboard2/SingleMeasCard_TransInfo.vue</t>
+          <t>partials/modeview/dashboard2/SingleMeasCard_PQ.vue</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>partials/dashboard2/SingleMeasCard_TransInfo.vue</t>
+          <t>partials/dashboard2/SingleMeasCard_PQ.vue</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -26386,17 +26458,17 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>(공통),/diagnosis</t>
+          <t>(공통),/</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>partials/modeview/diagnosis/BarChart_Event_Claude.vue</t>
+          <t>partials/modeview/dashboard2/SingleMeasCard_TransInfo.vue</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>partials/diagnosis/BarChart_Event_Claude.vue</t>
+          <t>partials/dashboard2/SingleMeasCard_TransInfo.vue</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -26416,12 +26488,12 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>partials/modeview/diagnosis/BarChart_FaultEvent.vue</t>
+          <t>partials/modeview/diagnosis/BarChart_Event_Claude.vue</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>partials/diagnosis/BarChart_FaultEvent.vue</t>
+          <t>partials/diagnosis/BarChart_Event_Claude.vue</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -26441,17 +26513,17 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>partials/modeview/diagnosis/DiagnosisTab.vue</t>
+          <t>partials/modeview/diagnosis/BarChart_FaultEvent.vue</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>partials/diagnosis/DiagnosisTab_mode.vue</t>
+          <t>partials/diagnosis/BarChart_FaultEvent.vue</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>이름변경</t>
+          <t>이동</t>
         </is>
       </c>
     </row>
@@ -26466,17 +26538,17 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>partials/modeview/diagnosis/DiagnosisTab_Bands.vue</t>
+          <t>partials/modeview/diagnosis/DiagnosisTab.vue</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>partials/diagnosis/DiagnosisTab_Bands.vue</t>
+          <t>partials/diagnosis/DiagnosisTab_mode.vue</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>이동</t>
+          <t>이름변경</t>
         </is>
       </c>
     </row>
@@ -26491,12 +26563,12 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>partials/modeview/diagnosis/DiagnosisTab_Bands_Legacy.vue</t>
+          <t>partials/modeview/diagnosis/DiagnosisTab_Bands.vue</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>partials/diagnosis/DiagnosisTab_Bands_Legacy.vue</t>
+          <t>partials/diagnosis/DiagnosisTab_Bands.vue</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -26516,12 +26588,12 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>partials/modeview/diagnosis/DiagnosisTab_Chart.vue</t>
+          <t>partials/modeview/diagnosis/DiagnosisTab_Bands_Legacy.vue</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>partials/diagnosis/DiagnosisTab_Chart.vue</t>
+          <t>partials/diagnosis/DiagnosisTab_Bands_Legacy.vue</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -26541,17 +26613,17 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>partials/modeview/diagnosis/Diagnosis_BarChart2.vue</t>
+          <t>partials/modeview/diagnosis/DiagnosisTab_Chart.vue</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>partials/diagnosis/Diagnosis_BarChart2_mode.vue</t>
+          <t>partials/diagnosis/DiagnosisTab_Chart.vue</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>이름변경</t>
+          <t>이동</t>
         </is>
       </c>
     </row>
@@ -26566,17 +26638,17 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>partials/modeview/diagnosis/Diagnosis_Info.vue</t>
+          <t>partials/modeview/diagnosis/Diagnosis_BarChart2.vue</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>partials/diagnosis/Diagnosis_Info.vue</t>
+          <t>partials/diagnosis/Diagnosis_BarChart2_mode.vue</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>이동</t>
+          <t>이름변경</t>
         </is>
       </c>
     </row>
@@ -26586,17 +26658,17 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>(공통),/meter</t>
+          <t>(공통),/diagnosis</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>partials/modeview/meter/CanvasAngle4.vue</t>
+          <t>partials/modeview/diagnosis/Diagnosis_Info.vue</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>partials/meter/CanvasAngle4.vue</t>
+          <t>partials/diagnosis/Diagnosis_Info.vue</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -26616,12 +26688,12 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>partials/modeview/meter/Meter.vue</t>
+          <t>partials/modeview/meter/CanvasAngle4.vue</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>partials/meter/Meter.vue</t>
+          <t>partials/meter/CanvasAngle4.vue</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -26641,12 +26713,12 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>partials/modeview/meter/MeterDetail2.vue</t>
+          <t>partials/modeview/meter/Meter.vue</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>partials/meter/MeterDetail2.vue</t>
+          <t>partials/meter/Meter.vue</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -26666,12 +26738,12 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>partials/modeview/meter/MeterKwh.vue</t>
+          <t>partials/modeview/meter/MeterDetail2.vue</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>partials/meter/MeterKwh.vue</t>
+          <t>partials/meter/MeterDetail2.vue</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -26691,12 +26763,12 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>partials/modeview/meter/MeterTable2.vue</t>
+          <t>partials/modeview/meter/MeterKwh.vue</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>partials/meter/MeterTable2.vue</t>
+          <t>partials/meter/MeterKwh.vue</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -26716,12 +26788,12 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>partials/modeview/meter/MeterTable3.vue</t>
+          <t>partials/modeview/meter/MeterTable2.vue</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>partials/meter/MeterTable3.vue</t>
+          <t>partials/meter/MeterTable2.vue</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -26741,12 +26813,12 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>partials/modeview/meter/MeterTable4.vue</t>
+          <t>partials/modeview/meter/MeterTable3.vue</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>partials/meter/MeterTable4.vue</t>
+          <t>partials/meter/MeterTable3.vue</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -26761,17 +26833,17 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>(공통),/powerq</t>
+          <t>(공통),/meter</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>partials/modeview/power/PowerQ2.vue</t>
+          <t>partials/modeview/meter/MeterTable4.vue</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>partials/power/PowerQ2.vue</t>
+          <t>partials/meter/MeterTable4.vue</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -26786,17 +26858,17 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>(공통),/report</t>
+          <t>(공통),/powerq</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>partials/modeview/report/Report_Diagnosis.vue</t>
+          <t>partials/modeview/power/PowerQ2.vue</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>partials/report/Report_Diagnosis.vue</t>
+          <t>partials/power/PowerQ2.vue</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -26816,12 +26888,12 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>partials/modeview/report/Report_Info.vue</t>
+          <t>partials/modeview/report/Report_Diagnosis.vue</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>partials/report/Report_Info.vue</t>
+          <t>partials/report/Report_Diagnosis.vue</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -26841,17 +26913,17 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>partials/modeview/report/Report_PQ.vue</t>
+          <t>partials/modeview/report/Report_Info.vue</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>partials/report/Report_PQ_mode.vue</t>
+          <t>partials/report/Report_Info.vue</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>이름변경</t>
+          <t>이동</t>
         </is>
       </c>
     </row>
@@ -26861,22 +26933,22 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>(공통)</t>
+          <t>(공통),/report</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>router_ko.js</t>
+          <t>partials/modeview/report/Report_PQ.vue</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>router_ko.js</t>
+          <t>partials/report/Report_PQ_mode.vue</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>그대로</t>
+          <t>이름변경</t>
         </is>
       </c>
     </row>
@@ -26886,17 +26958,17 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>(공통),/,/config,/diagnosis,/event,/master,/meter,/powerq,/report,/settings,/signin,/signup,/trend</t>
+          <t>(공통)</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>store/auth.js</t>
+          <t>router_ko.js</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>store/auth.js</t>
+          <t>router_ko.js</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -26911,17 +26983,17 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>(공통),/</t>
+          <t>(공통),/,/config,/diagnosis,/event,/master,/meter,/powerq,/report,/settings,/signin,/signup,/trend</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>store/realtime.js</t>
+          <t>store/auth.js</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>store/realtime.js</t>
+          <t>store/auth.js</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -26936,17 +27008,17 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>(공통),/,/config,/diagnosis,/event,/master,/meter,/powerq,/report,/settings,/signin,/signup,/trend</t>
+          <t>(공통),/</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>store/setup.js</t>
+          <t>store/realtime.js</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>store/setup.js</t>
+          <t>store/realtime.js</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -26961,17 +27033,17 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>(공통),/,/diagnosis,/meter,/powerq,/report,/trend</t>
+          <t>(공통),/,/config,/diagnosis,/event,/master,/meter,/powerq,/report,/settings,/signin,/signup,/trend</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>utils/Utils.js</t>
+          <t>store/setup.js</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>utils/Utils.js</t>
+          <t>store/setup.js</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -26986,20 +27058,45 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
+          <t>(공통),/,/diagnosis,/meter,/powerq,/report,/trend</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>utils/Utils.js</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>utils/Utils.js</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>그대로</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>197</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
           <t>(공통),/settings</t>
         </is>
       </c>
-      <c r="C197" t="inlineStr">
+      <c r="C198" t="inlineStr">
         <is>
           <t>utils/validation.js</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr">
+      <c r="D198" t="inlineStr">
         <is>
           <t>utils/validation.js</t>
         </is>
       </c>
-      <c r="E197" t="inlineStr">
+      <c r="E198" t="inlineStr">
         <is>
           <t>그대로</t>
         </is>
